--- a/data/June.xlsx
+++ b/data/June.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71BADAC3-DB52-4571-BC3D-173E01CD15FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,34 +15,31 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Author</author>
+    <author>ผู้สร้าง</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
+            <sz val="12"/>
             <rFont val="Arial"/>
-            <color/>
-            <sz val="12"/>
           </rPr>
-          <t xml:space="preserve">This is a reach-based metric. Reach-based metrics are de-duplicated metrics so you might see different numbers based on the level at which you are viewing data.</t>
+          <t>This is a reach-based metric. Reach-based metrics are de-duplicated metrics so you might see different numbers based on the level at which you are viewing data.</t>
         </r>
         <r>
           <rPr>
+            <sz val="12"/>
             <rFont val="Arial"/>
-            <color/>
-            <sz val="12"/>
           </rPr>
           <t xml:space="preserve">     </t>
         </r>
         <r>
           <rPr>
+            <sz val="12"/>
             <rFont val="Arial"/>
-            <color/>
-            <sz val="12"/>
           </rPr>
           <t xml:space="preserve">     </t>
         </r>
@@ -52,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="179">
   <si>
     <t>Ad name</t>
   </si>
@@ -258,9 +256,6 @@
     <t>หมดกองนี้ ลูกค้ารับไปเลย 23,XXX บาท</t>
   </si>
   <si>
-    <t>Total of 97 results</t>
-  </si>
-  <si>
     <t>Primary status</t>
   </si>
   <si>
@@ -538,9 +533,6 @@
   </si>
   <si>
     <t>2532.61</t>
-  </si>
-  <si>
-    <t>61339.65</t>
   </si>
   <si>
     <t>Reach</t>
@@ -600,8 +592,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -609,17 +601,19 @@
       <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="12"/>
-      <color/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
-      <color/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -657,136 +651,140 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<theme xmlns="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
-  <themeElements>
-    <clrScheme name="Office">
-      <dk1>
-        <sysClr val="windowText" lastClr="000000"/>
-      </dk1>
-      <lt1>
-        <sysClr val="window" lastClr="FFFFFF"/>
-      </lt1>
-      <dk2>
-        <srgbClr val="44546A"/>
-      </dk2>
-      <lt2>
-        <srgbClr val="E7E6E6"/>
-      </lt2>
-      <accent1>
-        <srgbClr val="5B9BD5"/>
-      </accent1>
-      <accent2>
-        <srgbClr val="ED7D31"/>
-      </accent2>
-      <accent3>
-        <srgbClr val="A5A5A5"/>
-      </accent3>
-      <accent4>
-        <srgbClr val="FFC000"/>
-      </accent4>
-      <accent5>
-        <srgbClr val="4472C4"/>
-      </accent5>
-      <accent6>
-        <srgbClr val="70AD47"/>
-      </accent6>
-      <hlink>
-        <srgbClr val="0563C1"/>
-      </hlink>
-      <folHlink>
-        <srgbClr val="954F72"/>
-      </folHlink>
-    </clrScheme>
-    <fontScheme name="Office">
-      <majorFont>
-        <latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <ea typeface=""/>
-        <cs typeface=""/>
-        <font script="Jpan" typeface="游ゴシック Light"/>
-        <font script="Hang" typeface="맑은 고딕"/>
-        <font script="Hans" typeface="等线 Light"/>
-        <font script="Hant" typeface="新細明體"/>
-        <font script="Arab" typeface="Times New Roman"/>
-        <font script="Hebr" typeface="Times New Roman"/>
-        <font script="Thai" typeface="Tahoma"/>
-        <font script="Ethi" typeface="Nyala"/>
-        <font script="Beng" typeface="Vrinda"/>
-        <font script="Gujr" typeface="Shruti"/>
-        <font script="Khmr" typeface="MoolBoran"/>
-        <font script="Knda" typeface="Tunga"/>
-        <font script="Guru" typeface="Raavi"/>
-        <font script="Cans" typeface="Euphemia"/>
-        <font script="Cher" typeface="Plantagenet Cherokee"/>
-        <font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <font script="Tibt" typeface="Microsoft Himalaya"/>
-        <font script="Thaa" typeface="MV Boli"/>
-        <font script="Deva" typeface="Mangal"/>
-        <font script="Telu" typeface="Gautami"/>
-        <font script="Taml" typeface="Latha"/>
-        <font script="Syrc" typeface="Estrangelo Edessa"/>
-        <font script="Orya" typeface="Kalinga"/>
-        <font script="Mlym" typeface="Kartika"/>
-        <font script="Laoo" typeface="DokChampa"/>
-        <font script="Sinh" typeface="Iskoola Pota"/>
-        <font script="Mong" typeface="Mongolian Baiti"/>
-        <font script="Viet" typeface="Times New Roman"/>
-        <font script="Uigh" typeface="Microsoft Uighur"/>
-        <font script="Geor" typeface="Sylfaen"/>
-      </majorFont>
-      <minorFont>
-        <latin typeface="Calibri" panose="020F0502020204030204"/>
-        <ea typeface=""/>
-        <cs typeface=""/>
-        <font script="Jpan" typeface="游ゴシック"/>
-        <font script="Hang" typeface="맑은 고딕"/>
-        <font script="Hans" typeface="等线"/>
-        <font script="Hant" typeface="新細明體"/>
-        <font script="Arab" typeface="Arial"/>
-        <font script="Hebr" typeface="Arial"/>
-        <font script="Thai" typeface="Tahoma"/>
-        <font script="Ethi" typeface="Nyala"/>
-        <font script="Beng" typeface="Vrinda"/>
-        <font script="Gujr" typeface="Shruti"/>
-        <font script="Khmr" typeface="DaunPenh"/>
-        <font script="Knda" typeface="Tunga"/>
-        <font script="Guru" typeface="Raavi"/>
-        <font script="Cans" typeface="Euphemia"/>
-        <font script="Cher" typeface="Plantagenet Cherokee"/>
-        <font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <font script="Tibt" typeface="Microsoft Himalaya"/>
-        <font script="Thaa" typeface="MV Boli"/>
-        <font script="Deva" typeface="Mangal"/>
-        <font script="Telu" typeface="Gautami"/>
-        <font script="Taml" typeface="Latha"/>
-        <font script="Syrc" typeface="Estrangelo Edessa"/>
-        <font script="Orya" typeface="Kalinga"/>
-        <font script="Mlym" typeface="Kartika"/>
-        <font script="Laoo" typeface="DokChampa"/>
-        <font script="Sinh" typeface="Iskoola Pota"/>
-        <font script="Mong" typeface="Mongolian Baiti"/>
-        <font script="Viet" typeface="Arial"/>
-        <font script="Uigh" typeface="Microsoft Uighur"/>
-        <font script="Geor" typeface="Sylfaen"/>
-      </minorFont>
-    </fontScheme>
-    <fmtScheme name="Office">
-      <fillStyleLst>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -842,8 +840,8 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-      </fillStyleLst>
-      <lnStyleLst>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -865,8 +863,8 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-      </lnStyleLst>
-      <effectStyleLst>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst/>
         </a:effectStyle>
@@ -882,8 +880,8 @@
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
-      </effectStyleLst>
-      <bgFillStyleLst>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -920,96 +918,99 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-      </bgFillStyleLst>
-    </fmtScheme>
-  </themeElements>
-  <objectDefaults/>
-  <extraClrSchemeLst/>
-</theme>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T98"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="38.77734375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="T1" s="1" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F2" s="2">
         <v>283</v>
@@ -1045,33 +1046,33 @@
         <v>2</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F3" s="2">
         <v>329</v>
@@ -1107,33 +1108,33 @@
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F4" s="2">
         <v>61149</v>
@@ -1169,33 +1170,33 @@
         <v>12</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F5" s="2">
         <v>1340</v>
@@ -1231,33 +1232,33 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F6" s="2">
         <v>27724</v>
@@ -1293,33 +1294,33 @@
         <v>6</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F7" s="2">
         <v>5270</v>
@@ -1355,33 +1356,33 @@
         <v>2</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F8" s="2">
         <v>14332</v>
@@ -1417,33 +1418,33 @@
         <v>2</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F9" s="2">
         <v>753</v>
@@ -1479,33 +1480,33 @@
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F10" s="2">
         <v>36896</v>
@@ -1541,33 +1542,33 @@
         <v>11</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F11" s="2">
         <v>353</v>
@@ -1603,33 +1604,33 @@
         <v>0</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F12" s="2">
         <v>5642</v>
@@ -1665,33 +1666,33 @@
         <v>0</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F13" s="2">
         <v>2518</v>
@@ -1727,33 +1728,33 @@
         <v>21</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F14" s="2">
         <v>35433</v>
@@ -1789,33 +1790,33 @@
         <v>12</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F15" s="2">
         <v>44051</v>
@@ -1851,33 +1852,33 @@
         <v>21</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F16" s="2">
         <v>1322</v>
@@ -1913,33 +1914,33 @@
         <v>19</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F17" s="2">
         <v>29256</v>
@@ -1975,33 +1976,33 @@
         <v>5</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F18" s="2">
         <v>6897</v>
@@ -2037,33 +2038,33 @@
         <v>1</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F19" s="2">
         <v>9735</v>
@@ -2099,33 +2100,33 @@
         <v>0</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F20" s="2">
         <v>35</v>
@@ -2161,33 +2162,33 @@
         <v>0</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F21" s="2">
         <v>1309</v>
@@ -2223,33 +2224,33 @@
         <v>17</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F22" s="2">
         <v>18740</v>
@@ -2285,33 +2286,33 @@
         <v>7</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F23" s="2">
         <v>29924</v>
@@ -2347,33 +2348,33 @@
         <v>1</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F24" s="2">
         <v>19311</v>
@@ -2409,33 +2410,33 @@
         <v>3</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F25" s="2">
         <v>3758</v>
@@ -2471,33 +2472,33 @@
         <v>68</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F26" s="2">
         <v>1028</v>
@@ -2533,33 +2534,33 @@
         <v>0</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F27" s="2">
         <v>802</v>
@@ -2595,33 +2596,33 @@
         <v>30</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F28" s="2">
         <v>57105</v>
@@ -2657,33 +2658,33 @@
         <v>12</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F29" s="2">
         <v>1607</v>
@@ -2719,33 +2720,33 @@
         <v>24</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F30" s="2">
         <v>6516</v>
@@ -2781,33 +2782,33 @@
         <v>4</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F31" s="2">
         <v>12435</v>
@@ -2843,33 +2844,33 @@
         <v>2</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F32" s="2">
         <v>1474</v>
@@ -2905,33 +2906,33 @@
         <v>20</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F33" s="2">
         <v>27810</v>
@@ -2967,33 +2968,33 @@
         <v>6</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F34" s="2">
         <v>5151</v>
@@ -3029,33 +3030,33 @@
         <v>0</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F35" s="2">
         <v>1540</v>
@@ -3091,33 +3092,33 @@
         <v>11</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F36" s="2">
         <v>20551</v>
@@ -3153,33 +3154,33 @@
         <v>2</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F37" s="2">
         <v>7845</v>
@@ -3215,33 +3216,33 @@
         <v>61</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F38" s="2">
         <v>76244</v>
@@ -3277,33 +3278,33 @@
         <v>17</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F39" s="2">
         <v>479</v>
@@ -3339,33 +3340,33 @@
         <v>0</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F40" s="2">
         <v>2010</v>
@@ -3401,33 +3402,33 @@
         <v>24</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F41" s="2">
         <v>7991</v>
@@ -3463,33 +3464,33 @@
         <v>2</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F42" s="2">
         <v>11514</v>
@@ -3525,33 +3526,33 @@
         <v>89</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F43" s="2">
         <v>54355</v>
@@ -3587,33 +3588,33 @@
         <v>15</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F44" s="2">
         <v>11308</v>
@@ -3649,33 +3650,33 @@
         <v>5</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F45" s="2">
         <v>1767</v>
@@ -3711,33 +3712,33 @@
         <v>1</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T45" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F46" s="2">
         <v>17361</v>
@@ -3773,33 +3774,33 @@
         <v>6</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="47">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F47" s="2">
         <v>1321</v>
@@ -3835,33 +3836,33 @@
         <v>18</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R47" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T47" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F48" s="2">
         <v>12651</v>
@@ -3897,33 +3898,33 @@
         <v>2</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T48" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F49" s="2">
         <v>1362</v>
@@ -3959,33 +3960,33 @@
         <v>16</v>
       </c>
       <c r="Q49" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R49" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F50" s="2">
         <v>6769</v>
@@ -4021,33 +4022,33 @@
         <v>0</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R50" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S50" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F51" s="2">
         <v>43588</v>
@@ -4083,33 +4084,33 @@
         <v>2</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T51" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F52" s="2">
         <v>8104</v>
@@ -4145,33 +4146,33 @@
         <v>64</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R52" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T52" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F53" s="2">
         <v>18717</v>
@@ -4207,33 +4208,33 @@
         <v>6</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S53" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T53" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F54" s="2">
         <v>101313</v>
@@ -4269,33 +4270,33 @@
         <v>37</v>
       </c>
       <c r="Q54" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R54" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S54" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T54" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="55">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F55" s="2">
         <v>741</v>
@@ -4331,33 +4332,33 @@
         <v>4</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R55" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S55" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T55" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F56" s="2">
         <v>1840</v>
@@ -4393,33 +4394,33 @@
         <v>26</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R56" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T56" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="57">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F57" s="2">
         <v>178886</v>
@@ -4455,33 +4456,33 @@
         <v>41</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R57" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T57" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="58">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F58" s="2">
         <v>394</v>
@@ -4517,33 +4518,33 @@
         <v>0</v>
       </c>
       <c r="Q58" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R58" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T58" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="59">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F59" s="2">
         <v>0</v>
@@ -4579,33 +4580,33 @@
         <v>0</v>
       </c>
       <c r="Q59" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R59" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T59" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="60">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F60" s="2">
         <v>0</v>
@@ -4641,33 +4642,33 @@
         <v>0</v>
       </c>
       <c r="Q60" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T60" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="61">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F61" s="2">
         <v>0</v>
@@ -4703,33 +4704,33 @@
         <v>0</v>
       </c>
       <c r="Q61" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R61" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F62" s="2">
         <v>0</v>
@@ -4765,33 +4766,33 @@
         <v>0</v>
       </c>
       <c r="Q62" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R62" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T62" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="63">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F63" s="2">
         <v>0</v>
@@ -4827,33 +4828,33 @@
         <v>0</v>
       </c>
       <c r="Q63" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R63" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T63" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="64">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F64" s="2">
         <v>0</v>
@@ -4889,33 +4890,33 @@
         <v>0</v>
       </c>
       <c r="Q64" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R64" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T64" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="65">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F65" s="2">
         <v>0</v>
@@ -4951,33 +4952,33 @@
         <v>0</v>
       </c>
       <c r="Q65" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R65" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T65" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="66">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F66" s="2">
         <v>0</v>
@@ -5013,33 +5014,33 @@
         <v>0</v>
       </c>
       <c r="Q66" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R66" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T66" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="67">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F67" s="2">
         <v>0</v>
@@ -5075,33 +5076,33 @@
         <v>0</v>
       </c>
       <c r="Q67" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R67" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S67" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T67" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="68">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F68" s="2">
         <v>0</v>
@@ -5137,33 +5138,33 @@
         <v>0</v>
       </c>
       <c r="Q68" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R68" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="69">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F69" s="2">
         <v>0</v>
@@ -5199,33 +5200,33 @@
         <v>0</v>
       </c>
       <c r="Q69" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R69" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S69" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T69" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="70">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F70" s="2">
         <v>0</v>
@@ -5261,33 +5262,33 @@
         <v>0</v>
       </c>
       <c r="Q70" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R70" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S70" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T70" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="71">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F71" s="2">
         <v>0</v>
@@ -5323,33 +5324,33 @@
         <v>0</v>
       </c>
       <c r="Q71" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R71" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S71" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T71" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="72">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F72" s="2">
         <v>0</v>
@@ -5385,33 +5386,33 @@
         <v>0</v>
       </c>
       <c r="Q72" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R72" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S72" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T72" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="73">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F73" s="2">
         <v>0</v>
@@ -5447,33 +5448,33 @@
         <v>0</v>
       </c>
       <c r="Q73" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R73" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S73" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T73" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="74">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F74" s="2">
         <v>0</v>
@@ -5509,33 +5510,33 @@
         <v>0</v>
       </c>
       <c r="Q74" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R74" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S74" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T74" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="75">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F75" s="2">
         <v>0</v>
@@ -5571,33 +5572,33 @@
         <v>0</v>
       </c>
       <c r="Q75" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R75" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S75" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T75" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="76">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F76" s="2">
         <v>0</v>
@@ -5633,33 +5634,33 @@
         <v>0</v>
       </c>
       <c r="Q76" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R76" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S76" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T76" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="77">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F77" s="2">
         <v>0</v>
@@ -5695,33 +5696,33 @@
         <v>0</v>
       </c>
       <c r="Q77" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R77" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S77" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T77" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="78">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F78" s="2">
         <v>0</v>
@@ -5757,33 +5758,33 @@
         <v>0</v>
       </c>
       <c r="Q78" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R78" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S78" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T78" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="79">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F79" s="2">
         <v>0</v>
@@ -5819,33 +5820,33 @@
         <v>0</v>
       </c>
       <c r="Q79" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R79" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S79" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T79" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="80">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F80" s="2">
         <v>0</v>
@@ -5881,33 +5882,33 @@
         <v>0</v>
       </c>
       <c r="Q80" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R80" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S80" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T80" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="81">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F81" s="2">
         <v>0</v>
@@ -5943,33 +5944,33 @@
         <v>0</v>
       </c>
       <c r="Q81" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R81" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S81" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T81" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="82">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F82" s="2">
         <v>0</v>
@@ -6005,33 +6006,33 @@
         <v>0</v>
       </c>
       <c r="Q82" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R82" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S82" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T82" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="83">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F83" s="2">
         <v>0</v>
@@ -6067,33 +6068,33 @@
         <v>0</v>
       </c>
       <c r="Q83" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R83" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S83" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T83" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="84">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F84" s="2">
         <v>0</v>
@@ -6129,33 +6130,33 @@
         <v>0</v>
       </c>
       <c r="Q84" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R84" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S84" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T84" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="85">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F85" s="2">
         <v>0</v>
@@ -6191,33 +6192,33 @@
         <v>0</v>
       </c>
       <c r="Q85" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R85" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S85" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T85" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="86">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F86" s="2">
         <v>0</v>
@@ -6253,33 +6254,33 @@
         <v>0</v>
       </c>
       <c r="Q86" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R86" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S86" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T86" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="87">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F87" s="2">
         <v>0</v>
@@ -6315,33 +6316,33 @@
         <v>0</v>
       </c>
       <c r="Q87" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R87" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S87" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T87" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="88">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F88" s="2">
         <v>0</v>
@@ -6377,33 +6378,33 @@
         <v>0</v>
       </c>
       <c r="Q88" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R88" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S88" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T88" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="89">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F89" s="2">
         <v>0</v>
@@ -6439,33 +6440,33 @@
         <v>0</v>
       </c>
       <c r="Q89" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R89" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S89" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T89" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="90">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F90" s="2">
         <v>0</v>
@@ -6501,33 +6502,33 @@
         <v>0</v>
       </c>
       <c r="Q90" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R90" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S90" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T90" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="91">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F91" s="2">
         <v>0</v>
@@ -6563,33 +6564,33 @@
         <v>0</v>
       </c>
       <c r="Q91" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R91" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S91" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T91" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="92">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F92" s="2">
         <v>0</v>
@@ -6625,33 +6626,33 @@
         <v>0</v>
       </c>
       <c r="Q92" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R92" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S92" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T92" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="93">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>65</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F93" s="2">
         <v>1498</v>
@@ -6687,33 +6688,33 @@
         <v>50</v>
       </c>
       <c r="Q93" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R93" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S93" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T93" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="94">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F94" s="2">
         <v>0</v>
@@ -6749,33 +6750,33 @@
         <v>0</v>
       </c>
       <c r="Q94" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R94" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S94" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T94" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="95">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F95" s="2">
         <v>0</v>
@@ -6811,33 +6812,33 @@
         <v>0</v>
       </c>
       <c r="Q95" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R95" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S95" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T95" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="96">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F96" s="2">
         <v>0</v>
@@ -6873,33 +6874,33 @@
         <v>0</v>
       </c>
       <c r="Q96" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R96" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S96" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T96" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="97">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F97" s="2">
         <v>0</v>
@@ -6935,33 +6936,33 @@
         <v>0</v>
       </c>
       <c r="Q97" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R97" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S97" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T97" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="98">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>65</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F98" s="2">
         <v>0</v>
@@ -6997,81 +6998,20 @@
         <v>0</v>
       </c>
       <c r="Q98" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R98" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S98" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T98" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F99" s="2">
-        <v>578351</v>
-      </c>
-      <c r="G99" s="2">
-        <v>1426815</v>
-      </c>
-      <c r="H99" s="2">
-        <v>1415455</v>
-      </c>
-      <c r="I99" s="2">
-        <v>894422</v>
-      </c>
-      <c r="J99" s="2">
-        <v>367658</v>
-      </c>
-      <c r="K99" s="2">
-        <v>6129</v>
-      </c>
-      <c r="L99" s="2">
-        <v>174</v>
-      </c>
-      <c r="M99" s="2">
-        <v>108</v>
-      </c>
-      <c r="N99" s="2">
-        <v>3546</v>
-      </c>
-      <c r="O99" s="2">
-        <v>3102</v>
-      </c>
-      <c r="P99" s="2">
-        <v>808</v>
-      </c>
-      <c r="Q99" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="R99" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="S99" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="T99" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/June.xlsx
+++ b/data/June.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71BADAC3-DB52-4571-BC3D-173E01CD15FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,31 +14,34 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>ผู้สร้าง</author>
+    <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
+            <rFont val="Arial"/>
+            <color/>
             <sz val="12"/>
-            <rFont val="Arial"/>
           </rPr>
-          <t>This is a reach-based metric. Reach-based metrics are de-duplicated metrics so you might see different numbers based on the level at which you are viewing data.</t>
+          <t xml:space="preserve">This is a reach-based metric. Reach-based metrics are de-duplicated metrics so you might see different numbers based on the level at which you are viewing data.</t>
         </r>
         <r>
           <rPr>
+            <rFont val="Arial"/>
+            <color/>
             <sz val="12"/>
-            <rFont val="Arial"/>
           </rPr>
           <t xml:space="preserve">     </t>
         </r>
         <r>
           <rPr>
+            <rFont val="Arial"/>
+            <color/>
             <sz val="12"/>
-            <rFont val="Arial"/>
           </rPr>
           <t xml:space="preserve">     </t>
         </r>
@@ -50,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
   <si>
     <t>Ad name</t>
   </si>
@@ -256,15 +258,18 @@
     <t>หมดกองนี้ ลูกค้ารับไปเลย 23,XXX บาท</t>
   </si>
   <si>
+    <t>Total of 97 results</t>
+  </si>
+  <si>
     <t>Primary status</t>
   </si>
   <si>
+    <t>Not delivering</t>
+  </si>
+  <si>
     <t>Active</t>
   </si>
   <si>
-    <t>Not delivering</t>
-  </si>
-  <si>
     <t>Paused</t>
   </si>
   <si>
@@ -274,12 +279,12 @@
     <t>Secondary status</t>
   </si>
   <si>
+    <t>Out of campaign budget</t>
+  </si>
+  <si>
     <t>--</t>
   </si>
   <si>
-    <t>Out of campaign budget</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -382,31 +387,31 @@
     <t>Cost</t>
   </si>
   <si>
-    <t>162.12</t>
-  </si>
-  <si>
-    <t>86.36</t>
-  </si>
-  <si>
-    <t>1270.66</t>
-  </si>
-  <si>
-    <t>16.67</t>
-  </si>
-  <si>
-    <t>510.82</t>
-  </si>
-  <si>
-    <t>137.15</t>
-  </si>
-  <si>
-    <t>382.00</t>
-  </si>
-  <si>
-    <t>9.62</t>
-  </si>
-  <si>
-    <t>1146.66</t>
+    <t>387.05</t>
+  </si>
+  <si>
+    <t>216.87</t>
+  </si>
+  <si>
+    <t>3631.96</t>
+  </si>
+  <si>
+    <t>24.33</t>
+  </si>
+  <si>
+    <t>866.26</t>
+  </si>
+  <si>
+    <t>221.48</t>
+  </si>
+  <si>
+    <t>612.52</t>
+  </si>
+  <si>
+    <t>10.13</t>
+  </si>
+  <si>
+    <t>2017.03</t>
   </si>
   <si>
     <t>8.61</t>
@@ -415,67 +420,61 @@
     <t>222.44</t>
   </si>
   <si>
-    <t>1074.90</t>
-  </si>
-  <si>
-    <t>994.44</t>
-  </si>
-  <si>
-    <t>724.63</t>
-  </si>
-  <si>
     <t>1200.00</t>
   </si>
   <si>
-    <t>730.76</t>
-  </si>
-  <si>
-    <t>134.58</t>
-  </si>
-  <si>
-    <t>237.91</t>
-  </si>
-  <si>
-    <t>0.07</t>
-  </si>
-  <si>
-    <t>344.89</t>
-  </si>
-  <si>
-    <t>633.87</t>
-  </si>
-  <si>
-    <t>376.30</t>
-  </si>
-  <si>
-    <t>3743.83</t>
-  </si>
-  <si>
-    <t>21.73</t>
-  </si>
-  <si>
-    <t>1094.01</t>
-  </si>
-  <si>
-    <t>174.60</t>
-  </si>
-  <si>
-    <t>397.32</t>
-  </si>
-  <si>
-    <t>879.05</t>
-  </si>
-  <si>
-    <t>130.32</t>
-  </si>
-  <si>
-    <t>771.32</t>
-  </si>
-  <si>
-    <t>4633.61</t>
-  </si>
-  <si>
-    <t>2272.52</t>
+    <t>1501.06</t>
+  </si>
+  <si>
+    <t>1159.23</t>
+  </si>
+  <si>
+    <t>1099.10</t>
+  </si>
+  <si>
+    <t>304.11</t>
+  </si>
+  <si>
+    <t>317.61</t>
+  </si>
+  <si>
+    <t>0.32</t>
+  </si>
+  <si>
+    <t>571.03</t>
+  </si>
+  <si>
+    <t>930.57</t>
+  </si>
+  <si>
+    <t>498.77</t>
+  </si>
+  <si>
+    <t>4747.76</t>
+  </si>
+  <si>
+    <t>1523.37</t>
+  </si>
+  <si>
+    <t>211.92</t>
+  </si>
+  <si>
+    <t>440.78</t>
+  </si>
+  <si>
+    <t>1155.35</t>
+  </si>
+  <si>
+    <t>152.62</t>
+  </si>
+  <si>
+    <t>911.71</t>
+  </si>
+  <si>
+    <t>6483.83</t>
+  </si>
+  <si>
+    <t>2706.85</t>
   </si>
   <si>
     <t>15.74</t>
@@ -484,46 +483,46 @@
     <t>368.95</t>
   </si>
   <si>
-    <t>4550.52</t>
-  </si>
-  <si>
-    <t>2340.95</t>
-  </si>
-  <si>
-    <t>403.48</t>
-  </si>
-  <si>
-    <t>51.33</t>
-  </si>
-  <si>
-    <t>589.95</t>
+    <t>6330.88</t>
+  </si>
+  <si>
+    <t>3142.56</t>
+  </si>
+  <si>
+    <t>696.72</t>
+  </si>
+  <si>
+    <t>55.49</t>
+  </si>
+  <si>
+    <t>840.92</t>
   </si>
   <si>
     <t>361.60</t>
   </si>
   <si>
-    <t>180.44</t>
-  </si>
-  <si>
-    <t>915.35</t>
-  </si>
-  <si>
-    <t>4541.85</t>
-  </si>
-  <si>
-    <t>463.27</t>
-  </si>
-  <si>
-    <t>2534.65</t>
-  </si>
-  <si>
-    <t>408.13</t>
-  </si>
-  <si>
-    <t>1591.00</t>
-  </si>
-  <si>
-    <t>5361.84</t>
+    <t>181.17</t>
+  </si>
+  <si>
+    <t>1339.56</t>
+  </si>
+  <si>
+    <t>6388.13</t>
+  </si>
+  <si>
+    <t>619.61</t>
+  </si>
+  <si>
+    <t>3613.87</t>
+  </si>
+  <si>
+    <t>417.84</t>
+  </si>
+  <si>
+    <t>1697.87</t>
+  </si>
+  <si>
+    <t>5769.63</t>
   </si>
   <si>
     <t>4.22</t>
@@ -533,6 +532,9 @@
   </si>
   <si>
     <t>2532.61</t>
+  </si>
+  <si>
+    <t>79336.37</t>
   </si>
   <si>
     <t>Reach</t>
@@ -592,8 +594,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -601,19 +603,17 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
       <sz val="12"/>
+      <color/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
+      <color/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -651,140 +651,136 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+      <alignment/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="44546A"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="ED7D31"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="FFC000"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4472C4"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="70AD47"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0563C1"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="954F72"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
+<theme xmlns="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+  <themeElements>
+    <clrScheme name="Office">
+      <dk1>
+        <sysClr val="windowText" lastClr="000000"/>
+      </dk1>
+      <lt1>
+        <sysClr val="window" lastClr="FFFFFF"/>
+      </lt1>
+      <dk2>
+        <srgbClr val="44546A"/>
+      </dk2>
+      <lt2>
+        <srgbClr val="E7E6E6"/>
+      </lt2>
+      <accent1>
+        <srgbClr val="5B9BD5"/>
+      </accent1>
+      <accent2>
+        <srgbClr val="ED7D31"/>
+      </accent2>
+      <accent3>
+        <srgbClr val="A5A5A5"/>
+      </accent3>
+      <accent4>
+        <srgbClr val="FFC000"/>
+      </accent4>
+      <accent5>
+        <srgbClr val="4472C4"/>
+      </accent5>
+      <accent6>
+        <srgbClr val="70AD47"/>
+      </accent6>
+      <hlink>
+        <srgbClr val="0563C1"/>
+      </hlink>
+      <folHlink>
+        <srgbClr val="954F72"/>
+      </folHlink>
+    </clrScheme>
+    <fontScheme name="Office">
+      <majorFont>
+        <latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <ea typeface=""/>
+        <cs typeface=""/>
+        <font script="Jpan" typeface="游ゴシック Light"/>
+        <font script="Hang" typeface="맑은 고딕"/>
+        <font script="Hans" typeface="等线 Light"/>
+        <font script="Hant" typeface="新細明體"/>
+        <font script="Arab" typeface="Times New Roman"/>
+        <font script="Hebr" typeface="Times New Roman"/>
+        <font script="Thai" typeface="Tahoma"/>
+        <font script="Ethi" typeface="Nyala"/>
+        <font script="Beng" typeface="Vrinda"/>
+        <font script="Gujr" typeface="Shruti"/>
+        <font script="Khmr" typeface="MoolBoran"/>
+        <font script="Knda" typeface="Tunga"/>
+        <font script="Guru" typeface="Raavi"/>
+        <font script="Cans" typeface="Euphemia"/>
+        <font script="Cher" typeface="Plantagenet Cherokee"/>
+        <font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <font script="Tibt" typeface="Microsoft Himalaya"/>
+        <font script="Thaa" typeface="MV Boli"/>
+        <font script="Deva" typeface="Mangal"/>
+        <font script="Telu" typeface="Gautami"/>
+        <font script="Taml" typeface="Latha"/>
+        <font script="Syrc" typeface="Estrangelo Edessa"/>
+        <font script="Orya" typeface="Kalinga"/>
+        <font script="Mlym" typeface="Kartika"/>
+        <font script="Laoo" typeface="DokChampa"/>
+        <font script="Sinh" typeface="Iskoola Pota"/>
+        <font script="Mong" typeface="Mongolian Baiti"/>
+        <font script="Viet" typeface="Times New Roman"/>
+        <font script="Uigh" typeface="Microsoft Uighur"/>
+        <font script="Geor" typeface="Sylfaen"/>
+      </majorFont>
+      <minorFont>
+        <latin typeface="Calibri" panose="020F0502020204030204"/>
+        <ea typeface=""/>
+        <cs typeface=""/>
+        <font script="Jpan" typeface="游ゴシック"/>
+        <font script="Hang" typeface="맑은 고딕"/>
+        <font script="Hans" typeface="等线"/>
+        <font script="Hant" typeface="新細明體"/>
+        <font script="Arab" typeface="Arial"/>
+        <font script="Hebr" typeface="Arial"/>
+        <font script="Thai" typeface="Tahoma"/>
+        <font script="Ethi" typeface="Nyala"/>
+        <font script="Beng" typeface="Vrinda"/>
+        <font script="Gujr" typeface="Shruti"/>
+        <font script="Khmr" typeface="DaunPenh"/>
+        <font script="Knda" typeface="Tunga"/>
+        <font script="Guru" typeface="Raavi"/>
+        <font script="Cans" typeface="Euphemia"/>
+        <font script="Cher" typeface="Plantagenet Cherokee"/>
+        <font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <font script="Tibt" typeface="Microsoft Himalaya"/>
+        <font script="Thaa" typeface="MV Boli"/>
+        <font script="Deva" typeface="Mangal"/>
+        <font script="Telu" typeface="Gautami"/>
+        <font script="Taml" typeface="Latha"/>
+        <font script="Syrc" typeface="Estrangelo Edessa"/>
+        <font script="Orya" typeface="Kalinga"/>
+        <font script="Mlym" typeface="Kartika"/>
+        <font script="Laoo" typeface="DokChampa"/>
+        <font script="Sinh" typeface="Iskoola Pota"/>
+        <font script="Mong" typeface="Mongolian Baiti"/>
+        <font script="Viet" typeface="Arial"/>
+        <font script="Uigh" typeface="Microsoft Uighur"/>
+        <font script="Geor" typeface="Sylfaen"/>
+      </minorFont>
+    </fontScheme>
+    <fmtScheme name="Office">
+      <fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -840,8 +836,8 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
+      </fillStyleLst>
+      <lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -863,8 +859,8 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
+      </lnStyleLst>
+      <effectStyleLst>
         <a:effectStyle>
           <a:effectLst/>
         </a:effectStyle>
@@ -880,8 +876,8 @@
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
+      </effectStyleLst>
+      <bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -918,37 +914,34 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
+      </bgFillStyleLst>
+    </fmtScheme>
+  </themeElements>
+  <objectDefaults/>
+  <extraClrSchemeLst/>
+</theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T98"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="4" max="4" width="38.77734375" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>161</v>
@@ -996,54 +989,54 @@
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F2" s="2">
-        <v>283</v>
+        <v>495</v>
       </c>
       <c r="G2" s="2">
-        <v>326</v>
+        <v>586</v>
       </c>
       <c r="H2" s="2">
-        <v>310</v>
+        <v>556</v>
       </c>
       <c r="I2" s="2">
-        <v>111</v>
+        <v>199</v>
       </c>
       <c r="J2" s="2">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="K2" s="2">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="L2" s="2">
         <v>0</v>
       </c>
       <c r="M2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" s="2">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="O2" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P2" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>173</v>
@@ -1052,60 +1045,60 @@
         <v>175</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T2" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F3" s="2">
-        <v>329</v>
+        <v>529</v>
       </c>
       <c r="G3" s="2">
-        <v>371</v>
+        <v>628</v>
       </c>
       <c r="H3" s="2">
-        <v>357</v>
+        <v>603</v>
       </c>
       <c r="I3" s="2">
-        <v>124</v>
+        <v>203</v>
       </c>
       <c r="J3" s="2">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="K3" s="2">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="L3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2">
         <v>0</v>
       </c>
       <c r="N3" s="2">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="O3" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P3" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>173</v>
@@ -1114,60 +1107,60 @@
         <v>175</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T3" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F4" s="2">
-        <v>61149</v>
+        <v>144062</v>
       </c>
       <c r="G4" s="2">
-        <v>70805</v>
+        <v>184801</v>
       </c>
       <c r="H4" s="2">
-        <v>70407</v>
+        <v>183652</v>
       </c>
       <c r="I4" s="2">
-        <v>45953</v>
+        <v>120352</v>
       </c>
       <c r="J4" s="2">
-        <v>20230</v>
+        <v>52177</v>
       </c>
       <c r="K4" s="2">
-        <v>86</v>
+        <v>252</v>
       </c>
       <c r="L4" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N4" s="2">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="O4" s="2">
-        <v>118</v>
+        <v>325</v>
       </c>
       <c r="P4" s="2">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>173</v>
@@ -1176,45 +1169,45 @@
         <v>175</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T4" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F5" s="2">
-        <v>1340</v>
+        <v>1564</v>
       </c>
       <c r="G5" s="2">
-        <v>1358</v>
+        <v>1634</v>
       </c>
       <c r="H5" s="2">
-        <v>1353</v>
+        <v>1627</v>
       </c>
       <c r="I5" s="2">
-        <v>904</v>
+        <v>1105</v>
       </c>
       <c r="J5" s="2">
-        <v>244</v>
+        <v>336</v>
       </c>
       <c r="K5" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L5" s="2">
         <v>0</v>
@@ -1229,7 +1222,7 @@
         <v>3</v>
       </c>
       <c r="P5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>173</v>
@@ -1238,45 +1231,45 @@
         <v>175</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T5" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F6" s="2">
-        <v>27724</v>
+        <v>39669</v>
       </c>
       <c r="G6" s="2">
-        <v>33907</v>
+        <v>54167</v>
       </c>
       <c r="H6" s="2">
-        <v>33687</v>
+        <v>53802</v>
       </c>
       <c r="I6" s="2">
-        <v>20786</v>
+        <v>32830</v>
       </c>
       <c r="J6" s="2">
-        <v>9717</v>
+        <v>15034</v>
       </c>
       <c r="K6" s="2">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="L6" s="2">
         <v>0</v>
@@ -1285,13 +1278,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O6" s="2">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="P6" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>173</v>
@@ -1300,45 +1293,45 @@
         <v>175</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T6" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F7" s="2">
-        <v>5270</v>
+        <v>7287</v>
       </c>
       <c r="G7" s="2">
-        <v>6337</v>
+        <v>9357</v>
       </c>
       <c r="H7" s="2">
-        <v>6301</v>
+        <v>9303</v>
       </c>
       <c r="I7" s="2">
-        <v>4017</v>
+        <v>5997</v>
       </c>
       <c r="J7" s="2">
-        <v>1413</v>
+        <v>2134</v>
       </c>
       <c r="K7" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L7" s="2">
         <v>0</v>
@@ -1347,10 +1340,10 @@
         <v>0</v>
       </c>
       <c r="N7" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="P7" s="2">
         <v>2</v>
@@ -1362,60 +1355,60 @@
         <v>175</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F8" s="2">
+        <v>19454</v>
+      </c>
+      <c r="G8" s="2">
+        <v>28193</v>
+      </c>
+      <c r="H8" s="2">
+        <v>27983</v>
+      </c>
+      <c r="I8" s="2">
+        <v>13069</v>
+      </c>
+      <c r="J8" s="2">
+        <v>5011</v>
+      </c>
+      <c r="K8" s="2">
         <v>69</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F8" s="2">
-        <v>14332</v>
-      </c>
-      <c r="G8" s="2">
-        <v>18649</v>
-      </c>
-      <c r="H8" s="2">
-        <v>18510</v>
-      </c>
-      <c r="I8" s="2">
-        <v>8777</v>
-      </c>
-      <c r="J8" s="2">
-        <v>3373</v>
-      </c>
-      <c r="K8" s="2">
-        <v>46</v>
-      </c>
       <c r="L8" s="2">
         <v>0</v>
       </c>
       <c r="M8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O8" s="2">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="P8" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>173</v>
@@ -1424,42 +1417,42 @@
         <v>175</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T8" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F9" s="2">
-        <v>753</v>
+        <v>769</v>
       </c>
       <c r="G9" s="2">
-        <v>811</v>
+        <v>831</v>
       </c>
       <c r="H9" s="2">
-        <v>808</v>
+        <v>828</v>
       </c>
       <c r="I9" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="J9" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K9" s="2">
         <v>1</v>
@@ -1486,45 +1479,45 @@
         <v>175</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T9" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F10" s="2">
-        <v>36896</v>
+        <v>55903</v>
       </c>
       <c r="G10" s="2">
-        <v>59121</v>
+        <v>99747</v>
       </c>
       <c r="H10" s="2">
-        <v>58839</v>
+        <v>99264</v>
       </c>
       <c r="I10" s="2">
-        <v>38782</v>
+        <v>63948</v>
       </c>
       <c r="J10" s="2">
-        <v>18762</v>
+        <v>30043</v>
       </c>
       <c r="K10" s="2">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="L10" s="2">
         <v>0</v>
@@ -1533,13 +1526,13 @@
         <v>0</v>
       </c>
       <c r="N10" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="O10" s="2">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="P10" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>173</v>
@@ -1548,13 +1541,13 @@
         <v>175</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T10" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -1565,10 +1558,10 @@
         <v>75</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F11" s="2">
         <v>353</v>
@@ -1610,13 +1603,13 @@
         <v>175</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T11" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -1627,10 +1620,10 @@
         <v>75</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F12" s="2">
         <v>5642</v>
@@ -1672,60 +1665,60 @@
         <v>175</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T12" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F13" s="2">
-        <v>2518</v>
+        <v>2788</v>
       </c>
       <c r="G13" s="2">
-        <v>3559</v>
+        <v>4045</v>
       </c>
       <c r="H13" s="2">
-        <v>3440</v>
+        <v>3909</v>
       </c>
       <c r="I13" s="2">
-        <v>1440</v>
+        <v>1618</v>
       </c>
       <c r="J13" s="2">
-        <v>476</v>
+        <v>530</v>
       </c>
       <c r="K13" s="2">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="L13" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M13" s="2">
         <v>3</v>
       </c>
       <c r="N13" s="2">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="O13" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P13" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>173</v>
@@ -1734,61 +1727,61 @@
         <v>175</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T13" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F14" s="2">
-        <v>35433</v>
+        <v>46733</v>
       </c>
       <c r="G14" s="2">
-        <v>52783</v>
+        <v>78489</v>
       </c>
       <c r="H14" s="2">
-        <v>52310</v>
+        <v>77782</v>
       </c>
       <c r="I14" s="2">
-        <v>28312</v>
+        <v>41470</v>
       </c>
       <c r="J14" s="2">
-        <v>9358</v>
+        <v>13571</v>
       </c>
       <c r="K14" s="2">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="L14" s="2">
         <v>0</v>
       </c>
       <c r="M14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="2">
+        <v>20</v>
+      </c>
+      <c r="O14" s="2">
+        <v>151</v>
+      </c>
+      <c r="P14" s="2">
         <v>14</v>
       </c>
-      <c r="O14" s="2">
-        <v>99</v>
-      </c>
-      <c r="P14" s="2">
-        <v>12</v>
-      </c>
       <c r="Q14" s="2" t="s">
         <v>173</v>
       </c>
@@ -1796,60 +1789,60 @@
         <v>175</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T14" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15">
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F15" s="2">
-        <v>44051</v>
+        <v>62804</v>
       </c>
       <c r="G15" s="2">
-        <v>53109</v>
+        <v>82624</v>
       </c>
       <c r="H15" s="2">
-        <v>52759</v>
+        <v>82078</v>
       </c>
       <c r="I15" s="2">
-        <v>41995</v>
+        <v>64408</v>
       </c>
       <c r="J15" s="2">
-        <v>19100</v>
+        <v>28011</v>
       </c>
       <c r="K15" s="2">
-        <v>117</v>
+        <v>196</v>
       </c>
       <c r="L15" s="2">
         <v>1</v>
       </c>
       <c r="M15" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N15" s="2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="O15" s="2">
-        <v>137</v>
+        <v>209</v>
       </c>
       <c r="P15" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Q15" s="2" t="s">
         <v>173</v>
@@ -1858,13 +1851,13 @@
         <v>175</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T15" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16">
       <c r="A16" s="2" t="s">
         <v>13</v>
       </c>
@@ -1875,10 +1868,10 @@
         <v>75</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F16" s="2">
         <v>1322</v>
@@ -1920,60 +1913,60 @@
         <v>175</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T16" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17">
       <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>125</v>
       </c>
       <c r="F17" s="2">
-        <v>29256</v>
+        <v>39678</v>
       </c>
       <c r="G17" s="2">
-        <v>37836</v>
+        <v>55209</v>
       </c>
       <c r="H17" s="2">
-        <v>37586</v>
+        <v>54846</v>
       </c>
       <c r="I17" s="2">
-        <v>23731</v>
+        <v>34020</v>
       </c>
       <c r="J17" s="2">
-        <v>7982</v>
+        <v>11378</v>
       </c>
       <c r="K17" s="2">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="L17" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M17" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N17" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O17" s="2">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="P17" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>173</v>
@@ -1982,45 +1975,45 @@
         <v>175</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T17" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18">
       <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>126</v>
       </c>
       <c r="F18" s="2">
-        <v>6897</v>
+        <v>12714</v>
       </c>
       <c r="G18" s="2">
-        <v>7776</v>
+        <v>16385</v>
       </c>
       <c r="H18" s="2">
-        <v>7717</v>
+        <v>16251</v>
       </c>
       <c r="I18" s="2">
-        <v>4520</v>
+        <v>9076</v>
       </c>
       <c r="J18" s="2">
-        <v>1523</v>
+        <v>3227</v>
       </c>
       <c r="K18" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L18" s="2">
         <v>0</v>
@@ -2029,13 +2022,13 @@
         <v>0</v>
       </c>
       <c r="N18" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O18" s="2">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="P18" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>173</v>
@@ -2044,45 +2037,45 @@
         <v>175</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T18" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19">
       <c r="A19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>127</v>
       </c>
       <c r="F19" s="2">
-        <v>9735</v>
+        <v>12162</v>
       </c>
       <c r="G19" s="2">
-        <v>10900</v>
+        <v>14838</v>
       </c>
       <c r="H19" s="2">
-        <v>10834</v>
+        <v>14737</v>
       </c>
       <c r="I19" s="2">
-        <v>5937</v>
+        <v>8086</v>
       </c>
       <c r="J19" s="2">
-        <v>2040</v>
+        <v>2801</v>
       </c>
       <c r="K19" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L19" s="2">
         <v>0</v>
@@ -2094,10 +2087,10 @@
         <v>1</v>
       </c>
       <c r="O19" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="P19" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="2" t="s">
         <v>173</v>
@@ -2106,42 +2099,42 @@
         <v>175</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T19" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20">
       <c r="A20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>128</v>
       </c>
       <c r="F20" s="2">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="G20" s="2">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="H20" s="2">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="I20" s="2">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J20" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K20" s="2">
         <v>0</v>
@@ -2168,13 +2161,13 @@
         <v>175</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T20" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21">
       <c r="A21" s="2" t="s">
         <v>17</v>
       </c>
@@ -2185,10 +2178,10 @@
         <v>75</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F21" s="2">
         <v>1309</v>
@@ -2230,45 +2223,45 @@
         <v>175</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T21" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22">
       <c r="A22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>129</v>
       </c>
       <c r="F22" s="2">
-        <v>18740</v>
+        <v>28706</v>
       </c>
       <c r="G22" s="2">
-        <v>22143</v>
+        <v>36847</v>
       </c>
       <c r="H22" s="2">
-        <v>22006</v>
+        <v>36610</v>
       </c>
       <c r="I22" s="2">
-        <v>15159</v>
+        <v>24530</v>
       </c>
       <c r="J22" s="2">
-        <v>6415</v>
+        <v>10077</v>
       </c>
       <c r="K22" s="2">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="L22" s="2">
         <v>1</v>
@@ -2277,13 +2270,13 @@
         <v>0</v>
       </c>
       <c r="N22" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O22" s="2">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="P22" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q22" s="2" t="s">
         <v>173</v>
@@ -2292,45 +2285,45 @@
         <v>175</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T22" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23">
       <c r="A23" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>130</v>
       </c>
       <c r="F23" s="2">
-        <v>29924</v>
+        <v>42440</v>
       </c>
       <c r="G23" s="2">
-        <v>35396</v>
+        <v>52589</v>
       </c>
       <c r="H23" s="2">
-        <v>35209</v>
+        <v>52310</v>
       </c>
       <c r="I23" s="2">
-        <v>23783</v>
+        <v>34299</v>
       </c>
       <c r="J23" s="2">
-        <v>10554</v>
+        <v>15297</v>
       </c>
       <c r="K23" s="2">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="L23" s="2">
         <v>0</v>
@@ -2339,13 +2332,13 @@
         <v>0</v>
       </c>
       <c r="N23" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O23" s="2">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="P23" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q23" s="2" t="s">
         <v>173</v>
@@ -2354,48 +2347,48 @@
         <v>175</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T23" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24">
       <c r="A24" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>131</v>
       </c>
       <c r="F24" s="2">
-        <v>19311</v>
+        <v>23593</v>
       </c>
       <c r="G24" s="2">
-        <v>23983</v>
+        <v>31224</v>
       </c>
       <c r="H24" s="2">
-        <v>23853</v>
+        <v>31053</v>
       </c>
       <c r="I24" s="2">
-        <v>18582</v>
+        <v>23423</v>
       </c>
       <c r="J24" s="2">
-        <v>7321</v>
+        <v>9133</v>
       </c>
       <c r="K24" s="2">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="L24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2">
         <v>1</v>
@@ -2404,7 +2397,7 @@
         <v>4</v>
       </c>
       <c r="O24" s="2">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="P24" s="2">
         <v>3</v>
@@ -2416,60 +2409,60 @@
         <v>175</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T24" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25">
       <c r="A25" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>132</v>
       </c>
       <c r="F25" s="2">
-        <v>3758</v>
+        <v>4436</v>
       </c>
       <c r="G25" s="2">
-        <v>4910</v>
+        <v>6032</v>
       </c>
       <c r="H25" s="2">
-        <v>4686</v>
+        <v>5740</v>
       </c>
       <c r="I25" s="2">
-        <v>2063</v>
+        <v>2520</v>
       </c>
       <c r="J25" s="2">
-        <v>633</v>
+        <v>772</v>
       </c>
       <c r="K25" s="2">
-        <v>464</v>
+        <v>584</v>
       </c>
       <c r="L25" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M25" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N25" s="2">
-        <v>414</v>
+        <v>519</v>
       </c>
       <c r="O25" s="2">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="P25" s="2">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="Q25" s="2" t="s">
         <v>173</v>
@@ -2478,57 +2471,57 @@
         <v>175</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T25" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26">
       <c r="A26" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="F26" s="2">
-        <v>1028</v>
+        <v>1100</v>
       </c>
       <c r="G26" s="2">
-        <v>1233</v>
+        <v>1337</v>
       </c>
       <c r="H26" s="2">
-        <v>1220</v>
+        <v>1324</v>
       </c>
       <c r="I26" s="2">
-        <v>917</v>
+        <v>993</v>
       </c>
       <c r="J26" s="2">
-        <v>306</v>
+        <v>339</v>
       </c>
       <c r="K26" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L26" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2">
         <v>0</v>
       </c>
       <c r="N26" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P26" s="2">
         <v>0</v>
@@ -2540,13 +2533,13 @@
         <v>175</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T26" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27">
       <c r="A27" s="2" t="s">
         <v>22</v>
       </c>
@@ -2557,10 +2550,10 @@
         <v>75</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F27" s="2">
         <v>802</v>
@@ -2602,45 +2595,45 @@
         <v>175</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T27" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28">
       <c r="A28" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F28" s="2">
-        <v>57105</v>
+        <v>74114</v>
       </c>
       <c r="G28" s="2">
-        <v>78462</v>
+        <v>107921</v>
       </c>
       <c r="H28" s="2">
-        <v>78046</v>
+        <v>107331</v>
       </c>
       <c r="I28" s="2">
-        <v>56856</v>
+        <v>76941</v>
       </c>
       <c r="J28" s="2">
-        <v>28578</v>
+        <v>38026</v>
       </c>
       <c r="K28" s="2">
-        <v>109</v>
+        <v>158</v>
       </c>
       <c r="L28" s="2">
         <v>0</v>
@@ -2649,13 +2642,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O28" s="2">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="P28" s="2">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q28" s="2" t="s">
         <v>173</v>
@@ -2664,13 +2657,13 @@
         <v>175</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T28" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29">
       <c r="A29" s="2" t="s">
         <v>24</v>
       </c>
@@ -2681,10 +2674,10 @@
         <v>75</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F29" s="2">
         <v>1607</v>
@@ -2726,45 +2719,45 @@
         <v>175</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T29" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30">
       <c r="A30" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F30" s="2">
-        <v>6516</v>
+        <v>7734</v>
       </c>
       <c r="G30" s="2">
-        <v>8532</v>
+        <v>10655</v>
       </c>
       <c r="H30" s="2">
-        <v>8454</v>
+        <v>10562</v>
       </c>
       <c r="I30" s="2">
-        <v>5347</v>
+        <v>6678</v>
       </c>
       <c r="J30" s="2">
-        <v>2444</v>
+        <v>3074</v>
       </c>
       <c r="K30" s="2">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="L30" s="2">
         <v>0</v>
@@ -2773,14 +2766,14 @@
         <v>0</v>
       </c>
       <c r="N30" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O30" s="2">
+        <v>12</v>
+      </c>
+      <c r="P30" s="2">
         <v>6</v>
       </c>
-      <c r="P30" s="2">
-        <v>4</v>
-      </c>
       <c r="Q30" s="2" t="s">
         <v>173</v>
       </c>
@@ -2788,45 +2781,45 @@
         <v>175</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T30" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31">
       <c r="A31" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F31" s="2">
-        <v>12435</v>
+        <v>13338</v>
       </c>
       <c r="G31" s="2">
-        <v>16757</v>
+        <v>19104</v>
       </c>
       <c r="H31" s="2">
-        <v>16657</v>
+        <v>18993</v>
       </c>
       <c r="I31" s="2">
-        <v>12231</v>
+        <v>14043</v>
       </c>
       <c r="J31" s="2">
-        <v>5198</v>
+        <v>5894</v>
       </c>
       <c r="K31" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L31" s="2">
         <v>0</v>
@@ -2835,10 +2828,10 @@
         <v>1</v>
       </c>
       <c r="N31" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O31" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="P31" s="2">
         <v>2</v>
@@ -2850,13 +2843,13 @@
         <v>175</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T31" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32">
       <c r="A32" s="2" t="s">
         <v>26</v>
       </c>
@@ -2867,10 +2860,10 @@
         <v>75</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F32" s="2">
         <v>1474</v>
@@ -2912,45 +2905,45 @@
         <v>175</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T32" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33">
       <c r="A33" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F33" s="2">
+        <v>35072</v>
+      </c>
+      <c r="G33" s="2">
+        <v>53125</v>
+      </c>
+      <c r="H33" s="2">
+        <v>52669</v>
+      </c>
+      <c r="I33" s="2">
+        <v>29095</v>
+      </c>
+      <c r="J33" s="2">
+        <v>10219</v>
+      </c>
+      <c r="K33" s="2">
         <v>74</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F33" s="2">
-        <v>27810</v>
-      </c>
-      <c r="G33" s="2">
-        <v>38641</v>
-      </c>
-      <c r="H33" s="2">
-        <v>38318</v>
-      </c>
-      <c r="I33" s="2">
-        <v>21758</v>
-      </c>
-      <c r="J33" s="2">
-        <v>7744</v>
-      </c>
-      <c r="K33" s="2">
-        <v>47</v>
       </c>
       <c r="L33" s="2">
         <v>1</v>
@@ -2959,13 +2952,13 @@
         <v>0</v>
       </c>
       <c r="N33" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O33" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="P33" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q33" s="2" t="s">
         <v>173</v>
@@ -2974,45 +2967,45 @@
         <v>175</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T33" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34">
       <c r="A34" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F34" s="2">
-        <v>5151</v>
+        <v>5710</v>
       </c>
       <c r="G34" s="2">
-        <v>6183</v>
+        <v>7181</v>
       </c>
       <c r="H34" s="2">
-        <v>6146</v>
+        <v>7141</v>
       </c>
       <c r="I34" s="2">
-        <v>3687</v>
+        <v>4329</v>
       </c>
       <c r="J34" s="2">
-        <v>948</v>
+        <v>1109</v>
       </c>
       <c r="K34" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L34" s="2">
         <v>0</v>
@@ -3024,7 +3017,7 @@
         <v>2</v>
       </c>
       <c r="O34" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P34" s="2">
         <v>0</v>
@@ -3036,13 +3029,13 @@
         <v>175</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T34" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35">
       <c r="A35" s="2" t="s">
         <v>28</v>
       </c>
@@ -3053,10 +3046,10 @@
         <v>75</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F35" s="2">
         <v>1540</v>
@@ -3098,45 +3091,45 @@
         <v>175</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T35" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36">
       <c r="A36" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F36" s="2">
-        <v>20551</v>
+        <v>23506</v>
       </c>
       <c r="G36" s="2">
-        <v>25370</v>
+        <v>31084</v>
       </c>
       <c r="H36" s="2">
-        <v>25131</v>
+        <v>30789</v>
       </c>
       <c r="I36" s="2">
-        <v>13349</v>
+        <v>16383</v>
       </c>
       <c r="J36" s="2">
-        <v>3844</v>
+        <v>4777</v>
       </c>
       <c r="K36" s="2">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="L36" s="2">
         <v>0</v>
@@ -3148,10 +3141,10 @@
         <v>5</v>
       </c>
       <c r="O36" s="2">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="P36" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q36" s="2" t="s">
         <v>173</v>
@@ -3160,60 +3153,60 @@
         <v>175</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T36" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37">
       <c r="A37" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F37" s="2">
-        <v>7845</v>
+        <v>10626</v>
       </c>
       <c r="G37" s="2">
-        <v>13242</v>
+        <v>20035</v>
       </c>
       <c r="H37" s="2">
-        <v>12769</v>
+        <v>19337</v>
       </c>
       <c r="I37" s="2">
-        <v>3003</v>
+        <v>4452</v>
       </c>
       <c r="J37" s="2">
-        <v>871</v>
+        <v>1281</v>
       </c>
       <c r="K37" s="2">
-        <v>478</v>
+        <v>644</v>
       </c>
       <c r="L37" s="2">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M37" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="N37" s="2">
-        <v>384</v>
+        <v>528</v>
       </c>
       <c r="O37" s="2">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="P37" s="2">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="Q37" s="2" t="s">
         <v>173</v>
@@ -3222,60 +3215,60 @@
         <v>175</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T37" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38">
       <c r="A38" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F38" s="2">
-        <v>76244</v>
+        <v>87218</v>
       </c>
       <c r="G38" s="2">
-        <v>117152</v>
+        <v>145755</v>
       </c>
       <c r="H38" s="2">
-        <v>116187</v>
+        <v>144559</v>
       </c>
       <c r="I38" s="2">
-        <v>62742</v>
+        <v>75827</v>
       </c>
       <c r="J38" s="2">
-        <v>26008</v>
+        <v>31325</v>
       </c>
       <c r="K38" s="2">
-        <v>233</v>
+        <v>321</v>
       </c>
       <c r="L38" s="2">
         <v>1</v>
       </c>
       <c r="M38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O38" s="2">
-        <v>543</v>
+        <v>701</v>
       </c>
       <c r="P38" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Q38" s="2" t="s">
         <v>173</v>
@@ -3284,39 +3277,39 @@
         <v>175</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39">
       <c r="A39" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F39" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G39" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H39" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I39" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J39" s="2">
         <v>38</v>
@@ -3346,13 +3339,13 @@
         <v>175</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T39" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40">
       <c r="A40" s="2" t="s">
         <v>32</v>
       </c>
@@ -3363,10 +3356,10 @@
         <v>75</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F40" s="2">
         <v>2010</v>
@@ -3408,13 +3401,13 @@
         <v>175</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T40" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41">
       <c r="A41" s="2" t="s">
         <v>33</v>
       </c>
@@ -3425,10 +3418,10 @@
         <v>75</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F41" s="2">
         <v>7991</v>
@@ -3470,60 +3463,60 @@
         <v>175</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T41" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42">
       <c r="A42" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F42" s="2">
-        <v>11514</v>
+        <v>15059</v>
       </c>
       <c r="G42" s="2">
-        <v>19857</v>
+        <v>29241</v>
       </c>
       <c r="H42" s="2">
-        <v>19311</v>
+        <v>28427</v>
       </c>
       <c r="I42" s="2">
-        <v>5733</v>
+        <v>8225</v>
       </c>
       <c r="J42" s="2">
-        <v>2065</v>
+        <v>2984</v>
       </c>
       <c r="K42" s="2">
-        <v>540</v>
+        <v>739</v>
       </c>
       <c r="L42" s="2">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="M42" s="2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="N42" s="2">
-        <v>367</v>
+        <v>497</v>
       </c>
       <c r="O42" s="2">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="P42" s="2">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="Q42" s="2" t="s">
         <v>173</v>
@@ -3532,60 +3525,60 @@
         <v>175</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T42" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43">
       <c r="A43" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F43" s="2">
-        <v>54355</v>
+        <v>66090</v>
       </c>
       <c r="G43" s="2">
-        <v>87098</v>
+        <v>116376</v>
       </c>
       <c r="H43" s="2">
-        <v>86501</v>
+        <v>115550</v>
       </c>
       <c r="I43" s="2">
-        <v>44160</v>
+        <v>57826</v>
       </c>
       <c r="J43" s="2">
-        <v>19067</v>
+        <v>24616</v>
       </c>
       <c r="K43" s="2">
-        <v>161</v>
+        <v>216</v>
       </c>
       <c r="L43" s="2">
         <v>0</v>
       </c>
       <c r="M43" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N43" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="O43" s="2">
-        <v>121</v>
+        <v>165</v>
       </c>
       <c r="P43" s="2">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="Q43" s="2" t="s">
         <v>173</v>
@@ -3594,45 +3587,45 @@
         <v>175</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T43" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44">
       <c r="A44" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F44" s="2">
-        <v>11308</v>
+        <v>16502</v>
       </c>
       <c r="G44" s="2">
-        <v>18094</v>
+        <v>29971</v>
       </c>
       <c r="H44" s="2">
-        <v>17920</v>
+        <v>29688</v>
       </c>
       <c r="I44" s="2">
-        <v>7865</v>
+        <v>12779</v>
       </c>
       <c r="J44" s="2">
-        <v>3206</v>
+        <v>5176</v>
       </c>
       <c r="K44" s="2">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="L44" s="2">
         <v>1</v>
@@ -3641,13 +3634,13 @@
         <v>0</v>
       </c>
       <c r="N44" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O44" s="2">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="P44" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q44" s="2" t="s">
         <v>173</v>
@@ -3656,42 +3649,42 @@
         <v>175</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T44" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45">
       <c r="A45" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F45" s="2">
-        <v>1767</v>
+        <v>1924</v>
       </c>
       <c r="G45" s="2">
-        <v>2149</v>
+        <v>2407</v>
       </c>
       <c r="H45" s="2">
-        <v>2132</v>
+        <v>2387</v>
       </c>
       <c r="I45" s="2">
-        <v>914</v>
+        <v>1014</v>
       </c>
       <c r="J45" s="2">
-        <v>351</v>
+        <v>380</v>
       </c>
       <c r="K45" s="2">
         <v>10</v>
@@ -3718,45 +3711,45 @@
         <v>175</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T45" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46">
       <c r="A46" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F46" s="2">
-        <v>17361</v>
+        <v>21760</v>
       </c>
       <c r="G46" s="2">
-        <v>24281</v>
+        <v>32832</v>
       </c>
       <c r="H46" s="2">
-        <v>24104</v>
+        <v>32586</v>
       </c>
       <c r="I46" s="2">
-        <v>13864</v>
+        <v>18738</v>
       </c>
       <c r="J46" s="2">
-        <v>4647</v>
+        <v>6331</v>
       </c>
       <c r="K46" s="2">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="L46" s="2">
         <v>0</v>
@@ -3765,13 +3758,13 @@
         <v>0</v>
       </c>
       <c r="N46" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O46" s="2">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="P46" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q46" s="2" t="s">
         <v>173</v>
@@ -3780,13 +3773,13 @@
         <v>175</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T46" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47">
       <c r="A47" s="2" t="s">
         <v>38</v>
       </c>
@@ -3797,10 +3790,10 @@
         <v>75</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F47" s="2">
         <v>1321</v>
@@ -3842,39 +3835,39 @@
         <v>175</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T47" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="48" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48">
       <c r="A48" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F48" s="2">
-        <v>12651</v>
+        <v>12655</v>
       </c>
       <c r="G48" s="2">
-        <v>14179</v>
+        <v>14187</v>
       </c>
       <c r="H48" s="2">
-        <v>14076</v>
+        <v>14084</v>
       </c>
       <c r="I48" s="2">
-        <v>9959</v>
+        <v>9964</v>
       </c>
       <c r="J48" s="2">
         <v>3325</v>
@@ -3904,13 +3897,13 @@
         <v>175</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T48" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49">
       <c r="A49" s="2" t="s">
         <v>39</v>
       </c>
@@ -3921,10 +3914,10 @@
         <v>75</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F49" s="2">
         <v>1362</v>
@@ -3966,42 +3959,42 @@
         <v>175</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T49" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50">
       <c r="A50" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F50" s="2">
-        <v>6769</v>
+        <v>6803</v>
       </c>
       <c r="G50" s="2">
-        <v>7280</v>
+        <v>7324</v>
       </c>
       <c r="H50" s="2">
-        <v>7235</v>
+        <v>7279</v>
       </c>
       <c r="I50" s="2">
-        <v>4464</v>
+        <v>4493</v>
       </c>
       <c r="J50" s="2">
-        <v>1952</v>
+        <v>1962</v>
       </c>
       <c r="K50" s="2">
         <v>10</v>
@@ -4028,60 +4021,60 @@
         <v>175</v>
       </c>
       <c r="S50" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T50" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51">
       <c r="A51" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F51" s="2">
-        <v>43588</v>
+        <v>58243</v>
       </c>
       <c r="G51" s="2">
-        <v>57265</v>
+        <v>84930</v>
       </c>
       <c r="H51" s="2">
-        <v>56864</v>
+        <v>84332</v>
       </c>
       <c r="I51" s="2">
-        <v>33695</v>
+        <v>47945</v>
       </c>
       <c r="J51" s="2">
-        <v>16240</v>
+        <v>22915</v>
       </c>
       <c r="K51" s="2">
-        <v>108</v>
+        <v>169</v>
       </c>
       <c r="L51" s="2">
         <v>0</v>
       </c>
       <c r="M51" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N51" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O51" s="2">
-        <v>278</v>
+        <v>426</v>
       </c>
       <c r="P51" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q51" s="2" t="s">
         <v>173</v>
@@ -4090,60 +4083,60 @@
         <v>175</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T51" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="52" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52">
       <c r="A52" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F52" s="2">
-        <v>8104</v>
+        <v>11500</v>
       </c>
       <c r="G52" s="2">
-        <v>11153</v>
+        <v>17075</v>
       </c>
       <c r="H52" s="2">
-        <v>10768</v>
+        <v>16470</v>
       </c>
       <c r="I52" s="2">
-        <v>4274</v>
+        <v>6477</v>
       </c>
       <c r="J52" s="2">
-        <v>1805</v>
+        <v>2714</v>
       </c>
       <c r="K52" s="2">
-        <v>558</v>
+        <v>779</v>
       </c>
       <c r="L52" s="2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="M52" s="2">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="N52" s="2">
-        <v>399</v>
+        <v>549</v>
       </c>
       <c r="O52" s="2">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="P52" s="2">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="Q52" s="2" t="s">
         <v>173</v>
@@ -4152,60 +4145,60 @@
         <v>175</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T52" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="53" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53">
       <c r="A53" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F53" s="2">
-        <v>18717</v>
+        <v>24101</v>
       </c>
       <c r="G53" s="2">
-        <v>22798</v>
+        <v>31180</v>
       </c>
       <c r="H53" s="2">
-        <v>22608</v>
+        <v>30912</v>
       </c>
       <c r="I53" s="2">
-        <v>15627</v>
+        <v>21198</v>
       </c>
       <c r="J53" s="2">
-        <v>7422</v>
+        <v>9777</v>
       </c>
       <c r="K53" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L53" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M53" s="2">
         <v>0</v>
       </c>
       <c r="N53" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O53" s="2">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="P53" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q53" s="2" t="s">
         <v>173</v>
@@ -4214,60 +4207,60 @@
         <v>175</v>
       </c>
       <c r="S53" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T53" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="54" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54">
       <c r="A54" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F54" s="2">
-        <v>101313</v>
+        <v>132333</v>
       </c>
       <c r="G54" s="2">
-        <v>134082</v>
+        <v>192063</v>
       </c>
       <c r="H54" s="2">
-        <v>133467</v>
+        <v>191150</v>
       </c>
       <c r="I54" s="2">
-        <v>85448</v>
+        <v>119667</v>
       </c>
       <c r="J54" s="2">
-        <v>43213</v>
+        <v>58870</v>
       </c>
       <c r="K54" s="2">
-        <v>181</v>
+        <v>271</v>
       </c>
       <c r="L54" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2">
         <v>3</v>
       </c>
       <c r="N54" s="2">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="O54" s="2">
-        <v>243</v>
+        <v>348</v>
       </c>
       <c r="P54" s="2">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="Q54" s="2" t="s">
         <v>173</v>
@@ -4276,57 +4269,57 @@
         <v>175</v>
       </c>
       <c r="S54" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T54" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55">
       <c r="A55" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F55" s="2">
-        <v>741</v>
+        <v>781</v>
       </c>
       <c r="G55" s="2">
-        <v>948</v>
+        <v>1007</v>
       </c>
       <c r="H55" s="2">
-        <v>907</v>
+        <v>964</v>
       </c>
       <c r="I55" s="2">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="J55" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K55" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L55" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M55" s="2">
         <v>2</v>
       </c>
       <c r="N55" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O55" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P55" s="2">
         <v>4</v>
@@ -4338,60 +4331,60 @@
         <v>175</v>
       </c>
       <c r="S55" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T55" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56">
       <c r="A56" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F56" s="2">
-        <v>1840</v>
+        <v>1955</v>
       </c>
       <c r="G56" s="2">
-        <v>2257</v>
+        <v>2407</v>
       </c>
       <c r="H56" s="2">
-        <v>2123</v>
+        <v>2260</v>
       </c>
       <c r="I56" s="2">
-        <v>920</v>
+        <v>979</v>
       </c>
       <c r="J56" s="2">
-        <v>343</v>
+        <v>370</v>
       </c>
       <c r="K56" s="2">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="L56" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M56" s="2">
         <v>2</v>
       </c>
       <c r="N56" s="2">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="O56" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P56" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Q56" s="2" t="s">
         <v>173</v>
@@ -4400,45 +4393,45 @@
         <v>175</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T56" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57">
       <c r="A57" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F57" s="2">
-        <v>178886</v>
+        <v>187004</v>
       </c>
       <c r="G57" s="2">
-        <v>240950</v>
+        <v>258163</v>
       </c>
       <c r="H57" s="2">
-        <v>239703</v>
+        <v>256819</v>
       </c>
       <c r="I57" s="2">
-        <v>186522</v>
+        <v>199778</v>
       </c>
       <c r="J57" s="2">
-        <v>63197</v>
+        <v>67903</v>
       </c>
       <c r="K57" s="2">
-        <v>295</v>
+        <v>323</v>
       </c>
       <c r="L57" s="2">
         <v>1</v>
@@ -4447,13 +4440,13 @@
         <v>5</v>
       </c>
       <c r="N57" s="2">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="O57" s="2">
-        <v>384</v>
+        <v>421</v>
       </c>
       <c r="P57" s="2">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="Q57" s="2" t="s">
         <v>173</v>
@@ -4462,39 +4455,39 @@
         <v>175</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T57" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="58" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58">
       <c r="A58" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F58" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G58" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="H58" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="I58" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J58" s="2">
         <v>45</v>
@@ -4524,27 +4517,27 @@
         <v>175</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T58" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59">
       <c r="A59" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F59" s="2">
         <v>0</v>
@@ -4586,27 +4579,27 @@
         <v>175</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T59" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="60" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60">
       <c r="A60" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F60" s="2">
         <v>0</v>
@@ -4648,27 +4641,27 @@
         <v>175</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T60" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="61" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61">
       <c r="A61" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F61" s="2">
         <v>0</v>
@@ -4710,27 +4703,27 @@
         <v>175</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T61" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="62" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62">
       <c r="A62" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F62" s="2">
         <v>0</v>
@@ -4772,27 +4765,27 @@
         <v>175</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T62" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63">
       <c r="A63" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F63" s="2">
         <v>0</v>
@@ -4834,27 +4827,27 @@
         <v>175</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T63" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="64" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64">
       <c r="A64" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F64" s="2">
         <v>0</v>
@@ -4896,27 +4889,27 @@
         <v>175</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T64" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="65" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65">
       <c r="A65" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F65" s="2">
         <v>0</v>
@@ -4958,27 +4951,27 @@
         <v>175</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T65" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="66" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66">
       <c r="A66" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F66" s="2">
         <v>0</v>
@@ -5020,27 +5013,27 @@
         <v>175</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T66" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="67" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67">
       <c r="A67" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F67" s="2">
         <v>0</v>
@@ -5082,27 +5075,27 @@
         <v>175</v>
       </c>
       <c r="S67" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T67" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="68" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68">
       <c r="A68" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F68" s="2">
         <v>0</v>
@@ -5144,27 +5137,27 @@
         <v>175</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T68" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="69" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69">
       <c r="A69" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F69" s="2">
         <v>0</v>
@@ -5206,27 +5199,27 @@
         <v>175</v>
       </c>
       <c r="S69" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T69" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="70" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70">
       <c r="A70" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F70" s="2">
         <v>0</v>
@@ -5268,27 +5261,27 @@
         <v>175</v>
       </c>
       <c r="S70" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T70" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="71" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71">
       <c r="A71" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F71" s="2">
         <v>0</v>
@@ -5330,27 +5323,27 @@
         <v>175</v>
       </c>
       <c r="S71" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T71" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="72" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72">
       <c r="A72" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F72" s="2">
         <v>0</v>
@@ -5392,27 +5385,27 @@
         <v>175</v>
       </c>
       <c r="S72" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T72" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="73" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="73">
       <c r="A73" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F73" s="2">
         <v>0</v>
@@ -5454,27 +5447,27 @@
         <v>175</v>
       </c>
       <c r="S73" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T73" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="74" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74">
       <c r="A74" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F74" s="2">
         <v>0</v>
@@ -5516,27 +5509,27 @@
         <v>175</v>
       </c>
       <c r="S74" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T74" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="75" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75">
       <c r="A75" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F75" s="2">
         <v>0</v>
@@ -5578,27 +5571,27 @@
         <v>175</v>
       </c>
       <c r="S75" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T75" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="76" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76">
       <c r="A76" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F76" s="2">
         <v>0</v>
@@ -5640,27 +5633,27 @@
         <v>175</v>
       </c>
       <c r="S76" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T76" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="77" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77">
       <c r="A77" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F77" s="2">
         <v>0</v>
@@ -5702,27 +5695,27 @@
         <v>175</v>
       </c>
       <c r="S77" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T77" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="78" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="78">
       <c r="A78" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F78" s="2">
         <v>0</v>
@@ -5764,27 +5757,27 @@
         <v>175</v>
       </c>
       <c r="S78" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T78" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="79" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="79">
       <c r="A79" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F79" s="2">
         <v>0</v>
@@ -5826,27 +5819,27 @@
         <v>175</v>
       </c>
       <c r="S79" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T79" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="80" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="80">
       <c r="A80" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F80" s="2">
         <v>0</v>
@@ -5888,27 +5881,27 @@
         <v>175</v>
       </c>
       <c r="S80" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T80" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="81" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="81">
       <c r="A81" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F81" s="2">
         <v>0</v>
@@ -5950,27 +5943,27 @@
         <v>175</v>
       </c>
       <c r="S81" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T81" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82">
       <c r="A82" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F82" s="2">
         <v>0</v>
@@ -6012,13 +6005,13 @@
         <v>175</v>
       </c>
       <c r="S82" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T82" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="83">
       <c r="A83" s="2" t="s">
         <v>59</v>
       </c>
@@ -6026,13 +6019,13 @@
         <v>70</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F83" s="2">
         <v>0</v>
@@ -6074,13 +6067,13 @@
         <v>175</v>
       </c>
       <c r="S83" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T83" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="84">
       <c r="A84" s="2" t="s">
         <v>60</v>
       </c>
@@ -6088,13 +6081,13 @@
         <v>70</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F84" s="2">
         <v>0</v>
@@ -6136,27 +6129,27 @@
         <v>175</v>
       </c>
       <c r="S84" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T84" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="85">
       <c r="A85" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F85" s="2">
         <v>0</v>
@@ -6198,27 +6191,27 @@
         <v>175</v>
       </c>
       <c r="S85" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T85" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="86">
       <c r="A86" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F86" s="2">
         <v>0</v>
@@ -6260,27 +6253,27 @@
         <v>175</v>
       </c>
       <c r="S86" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T86" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="87">
       <c r="A87" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F87" s="2">
         <v>0</v>
@@ -6322,27 +6315,27 @@
         <v>175</v>
       </c>
       <c r="S87" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T87" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="88">
       <c r="A88" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F88" s="2">
         <v>0</v>
@@ -6384,27 +6377,27 @@
         <v>175</v>
       </c>
       <c r="S88" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T88" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="89" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="89">
       <c r="A89" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F89" s="2">
         <v>0</v>
@@ -6446,27 +6439,27 @@
         <v>175</v>
       </c>
       <c r="S89" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T89" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="90" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="90">
       <c r="A90" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F90" s="2">
         <v>0</v>
@@ -6508,27 +6501,27 @@
         <v>175</v>
       </c>
       <c r="S90" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T90" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="91" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="91">
       <c r="A91" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F91" s="2">
         <v>0</v>
@@ -6570,27 +6563,27 @@
         <v>175</v>
       </c>
       <c r="S91" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T91" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="92" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="92">
       <c r="A92" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F92" s="2">
         <v>0</v>
@@ -6632,27 +6625,27 @@
         <v>175</v>
       </c>
       <c r="S92" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T92" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="93" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="93">
       <c r="A93" s="2" t="s">
         <v>65</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F93" s="2">
         <v>1498</v>
@@ -6694,27 +6687,27 @@
         <v>175</v>
       </c>
       <c r="S93" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T93" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="94" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="94">
       <c r="A94" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F94" s="2">
         <v>0</v>
@@ -6756,27 +6749,27 @@
         <v>175</v>
       </c>
       <c r="S94" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T94" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="95" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="95">
       <c r="A95" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F95" s="2">
         <v>0</v>
@@ -6818,27 +6811,27 @@
         <v>175</v>
       </c>
       <c r="S95" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T95" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="96" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="96">
       <c r="A96" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F96" s="2">
         <v>0</v>
@@ -6880,27 +6873,27 @@
         <v>175</v>
       </c>
       <c r="S96" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T96" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="97" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="97">
       <c r="A97" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F97" s="2">
         <v>0</v>
@@ -6942,27 +6935,27 @@
         <v>175</v>
       </c>
       <c r="S97" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T97" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="98" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="98">
       <c r="A98" s="2" t="s">
         <v>65</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F98" s="2">
         <v>0</v>
@@ -7004,14 +6997,75 @@
         <v>175</v>
       </c>
       <c r="S98" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T98" s="2" t="s">
         <v>178</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F99" s="2">
+        <v>731609</v>
+      </c>
+      <c r="G99" s="2">
+        <v>2008384</v>
+      </c>
+      <c r="H99" s="2">
+        <v>1992409</v>
+      </c>
+      <c r="I99" s="2">
+        <v>1235116</v>
+      </c>
+      <c r="J99" s="2">
+        <v>508712</v>
+      </c>
+      <c r="K99" s="2">
+        <v>7896</v>
+      </c>
+      <c r="L99" s="2">
+        <v>217</v>
+      </c>
+      <c r="M99" s="2">
+        <v>146</v>
+      </c>
+      <c r="N99" s="2">
+        <v>4229</v>
+      </c>
+      <c r="O99" s="2">
+        <v>4526</v>
+      </c>
+      <c r="P99" s="2">
+        <v>1028</v>
+      </c>
+      <c r="Q99" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="R99" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="S99" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="T99" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/June.xlsx
+++ b/data/June.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D6C5727-9839-4DAD-B75C-59F90CE4FC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,34 +15,31 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Author</author>
+    <author>ผู้สร้าง</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
+            <sz val="12"/>
             <rFont val="Arial"/>
-            <color/>
-            <sz val="12"/>
           </rPr>
-          <t xml:space="preserve">This is a reach-based metric. Reach-based metrics are de-duplicated metrics so you might see different numbers based on the level at which you are viewing data.</t>
+          <t>This is a reach-based metric. Reach-based metrics are de-duplicated metrics so you might see different numbers based on the level at which you are viewing data.</t>
         </r>
         <r>
           <rPr>
+            <sz val="12"/>
             <rFont val="Arial"/>
-            <color/>
-            <sz val="12"/>
           </rPr>
           <t xml:space="preserve">     </t>
         </r>
         <r>
           <rPr>
+            <sz val="12"/>
             <rFont val="Arial"/>
-            <color/>
-            <sz val="12"/>
           </rPr>
           <t xml:space="preserve">     </t>
         </r>
@@ -52,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="177">
   <si>
     <t>Ad name</t>
   </si>
@@ -258,9 +256,6 @@
     <t>หมดกองนี้ ลูกค้ารับไปเลย 23,XXX บาท</t>
   </si>
   <si>
-    <t>Total of 97 results</t>
-  </si>
-  <si>
     <t>Primary status</t>
   </si>
   <si>
@@ -532,9 +527,6 @@
   </si>
   <si>
     <t>2532.61</t>
-  </si>
-  <si>
-    <t>79336.37</t>
   </si>
   <si>
     <t>Reach</t>
@@ -594,8 +586,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -603,17 +595,19 @@
       <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="12"/>
-      <color/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
-      <color/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -651,136 +645,140 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<theme xmlns="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
-  <themeElements>
-    <clrScheme name="Office">
-      <dk1>
-        <sysClr val="windowText" lastClr="000000"/>
-      </dk1>
-      <lt1>
-        <sysClr val="window" lastClr="FFFFFF"/>
-      </lt1>
-      <dk2>
-        <srgbClr val="44546A"/>
-      </dk2>
-      <lt2>
-        <srgbClr val="E7E6E6"/>
-      </lt2>
-      <accent1>
-        <srgbClr val="5B9BD5"/>
-      </accent1>
-      <accent2>
-        <srgbClr val="ED7D31"/>
-      </accent2>
-      <accent3>
-        <srgbClr val="A5A5A5"/>
-      </accent3>
-      <accent4>
-        <srgbClr val="FFC000"/>
-      </accent4>
-      <accent5>
-        <srgbClr val="4472C4"/>
-      </accent5>
-      <accent6>
-        <srgbClr val="70AD47"/>
-      </accent6>
-      <hlink>
-        <srgbClr val="0563C1"/>
-      </hlink>
-      <folHlink>
-        <srgbClr val="954F72"/>
-      </folHlink>
-    </clrScheme>
-    <fontScheme name="Office">
-      <majorFont>
-        <latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <ea typeface=""/>
-        <cs typeface=""/>
-        <font script="Jpan" typeface="游ゴシック Light"/>
-        <font script="Hang" typeface="맑은 고딕"/>
-        <font script="Hans" typeface="等线 Light"/>
-        <font script="Hant" typeface="新細明體"/>
-        <font script="Arab" typeface="Times New Roman"/>
-        <font script="Hebr" typeface="Times New Roman"/>
-        <font script="Thai" typeface="Tahoma"/>
-        <font script="Ethi" typeface="Nyala"/>
-        <font script="Beng" typeface="Vrinda"/>
-        <font script="Gujr" typeface="Shruti"/>
-        <font script="Khmr" typeface="MoolBoran"/>
-        <font script="Knda" typeface="Tunga"/>
-        <font script="Guru" typeface="Raavi"/>
-        <font script="Cans" typeface="Euphemia"/>
-        <font script="Cher" typeface="Plantagenet Cherokee"/>
-        <font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <font script="Tibt" typeface="Microsoft Himalaya"/>
-        <font script="Thaa" typeface="MV Boli"/>
-        <font script="Deva" typeface="Mangal"/>
-        <font script="Telu" typeface="Gautami"/>
-        <font script="Taml" typeface="Latha"/>
-        <font script="Syrc" typeface="Estrangelo Edessa"/>
-        <font script="Orya" typeface="Kalinga"/>
-        <font script="Mlym" typeface="Kartika"/>
-        <font script="Laoo" typeface="DokChampa"/>
-        <font script="Sinh" typeface="Iskoola Pota"/>
-        <font script="Mong" typeface="Mongolian Baiti"/>
-        <font script="Viet" typeface="Times New Roman"/>
-        <font script="Uigh" typeface="Microsoft Uighur"/>
-        <font script="Geor" typeface="Sylfaen"/>
-      </majorFont>
-      <minorFont>
-        <latin typeface="Calibri" panose="020F0502020204030204"/>
-        <ea typeface=""/>
-        <cs typeface=""/>
-        <font script="Jpan" typeface="游ゴシック"/>
-        <font script="Hang" typeface="맑은 고딕"/>
-        <font script="Hans" typeface="等线"/>
-        <font script="Hant" typeface="新細明體"/>
-        <font script="Arab" typeface="Arial"/>
-        <font script="Hebr" typeface="Arial"/>
-        <font script="Thai" typeface="Tahoma"/>
-        <font script="Ethi" typeface="Nyala"/>
-        <font script="Beng" typeface="Vrinda"/>
-        <font script="Gujr" typeface="Shruti"/>
-        <font script="Khmr" typeface="DaunPenh"/>
-        <font script="Knda" typeface="Tunga"/>
-        <font script="Guru" typeface="Raavi"/>
-        <font script="Cans" typeface="Euphemia"/>
-        <font script="Cher" typeface="Plantagenet Cherokee"/>
-        <font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <font script="Tibt" typeface="Microsoft Himalaya"/>
-        <font script="Thaa" typeface="MV Boli"/>
-        <font script="Deva" typeface="Mangal"/>
-        <font script="Telu" typeface="Gautami"/>
-        <font script="Taml" typeface="Latha"/>
-        <font script="Syrc" typeface="Estrangelo Edessa"/>
-        <font script="Orya" typeface="Kalinga"/>
-        <font script="Mlym" typeface="Kartika"/>
-        <font script="Laoo" typeface="DokChampa"/>
-        <font script="Sinh" typeface="Iskoola Pota"/>
-        <font script="Mong" typeface="Mongolian Baiti"/>
-        <font script="Viet" typeface="Arial"/>
-        <font script="Uigh" typeface="Microsoft Uighur"/>
-        <font script="Geor" typeface="Sylfaen"/>
-      </minorFont>
-    </fontScheme>
-    <fmtScheme name="Office">
-      <fillStyleLst>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -836,8 +834,8 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-      </fillStyleLst>
-      <lnStyleLst>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -859,8 +857,8 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-      </lnStyleLst>
-      <effectStyleLst>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst/>
         </a:effectStyle>
@@ -876,8 +874,8 @@
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
-      </effectStyleLst>
-      <bgFillStyleLst>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -914,96 +912,96 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-      </bgFillStyleLst>
-    </fmtScheme>
-  </themeElements>
-  <objectDefaults/>
-  <extraClrSchemeLst/>
-</theme>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T98"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="T1" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F2" s="2">
         <v>495</v>
@@ -1039,33 +1037,33 @@
         <v>3</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F3" s="2">
         <v>529</v>
@@ -1101,33 +1099,33 @@
         <v>6</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F4" s="2">
         <v>144062</v>
@@ -1163,33 +1161,33 @@
         <v>28</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F5" s="2">
         <v>1564</v>
@@ -1225,33 +1223,33 @@
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F6" s="2">
         <v>39669</v>
@@ -1287,33 +1285,33 @@
         <v>8</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F7" s="2">
         <v>7287</v>
@@ -1349,33 +1347,33 @@
         <v>2</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F8" s="2">
         <v>19454</v>
@@ -1411,33 +1409,33 @@
         <v>4</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F9" s="2">
         <v>769</v>
@@ -1473,33 +1471,33 @@
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F10" s="2">
         <v>55903</v>
@@ -1535,33 +1533,33 @@
         <v>15</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F11" s="2">
         <v>353</v>
@@ -1597,33 +1595,33 @@
         <v>0</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F12" s="2">
         <v>5642</v>
@@ -1659,33 +1657,33 @@
         <v>0</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F13" s="2">
         <v>2788</v>
@@ -1721,33 +1719,33 @@
         <v>22</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F14" s="2">
         <v>46733</v>
@@ -1783,33 +1781,33 @@
         <v>14</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F15" s="2">
         <v>62804</v>
@@ -1845,33 +1843,33 @@
         <v>25</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F16" s="2">
         <v>1322</v>
@@ -1907,33 +1905,33 @@
         <v>19</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F17" s="2">
         <v>39678</v>
@@ -1969,33 +1967,33 @@
         <v>8</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F18" s="2">
         <v>12714</v>
@@ -2031,33 +2029,33 @@
         <v>3</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F19" s="2">
         <v>12162</v>
@@ -2093,33 +2091,33 @@
         <v>2</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F20" s="2">
         <v>56</v>
@@ -2155,33 +2153,33 @@
         <v>0</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F21" s="2">
         <v>1309</v>
@@ -2217,33 +2215,33 @@
         <v>17</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F22" s="2">
         <v>28706</v>
@@ -2279,33 +2277,33 @@
         <v>9</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F23" s="2">
         <v>42440</v>
@@ -2341,33 +2339,33 @@
         <v>4</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F24" s="2">
         <v>23593</v>
@@ -2403,33 +2401,33 @@
         <v>3</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F25" s="2">
         <v>4436</v>
@@ -2465,33 +2463,33 @@
         <v>85</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F26" s="2">
         <v>1100</v>
@@ -2527,33 +2525,33 @@
         <v>0</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F27" s="2">
         <v>802</v>
@@ -2589,33 +2587,33 @@
         <v>30</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F28" s="2">
         <v>74114</v>
@@ -2651,33 +2649,33 @@
         <v>22</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F29" s="2">
         <v>1607</v>
@@ -2713,33 +2711,33 @@
         <v>24</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F30" s="2">
         <v>7734</v>
@@ -2775,33 +2773,33 @@
         <v>6</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F31" s="2">
         <v>13338</v>
@@ -2837,33 +2835,33 @@
         <v>2</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F32" s="2">
         <v>1474</v>
@@ -2899,33 +2897,33 @@
         <v>20</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F33" s="2">
         <v>35072</v>
@@ -2961,33 +2959,33 @@
         <v>8</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F34" s="2">
         <v>5710</v>
@@ -3023,33 +3021,33 @@
         <v>0</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F35" s="2">
         <v>1540</v>
@@ -3085,33 +3083,33 @@
         <v>11</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F36" s="2">
         <v>23506</v>
@@ -3147,33 +3145,33 @@
         <v>3</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F37" s="2">
         <v>10626</v>
@@ -3209,33 +3207,33 @@
         <v>92</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F38" s="2">
         <v>87218</v>
@@ -3271,33 +3269,33 @@
         <v>22</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F39" s="2">
         <v>480</v>
@@ -3333,33 +3331,33 @@
         <v>0</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F40" s="2">
         <v>2010</v>
@@ -3395,33 +3393,33 @@
         <v>24</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F41" s="2">
         <v>7991</v>
@@ -3457,33 +3455,33 @@
         <v>2</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F42" s="2">
         <v>15059</v>
@@ -3519,33 +3517,33 @@
         <v>116</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F43" s="2">
         <v>66090</v>
@@ -3581,33 +3579,33 @@
         <v>23</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F44" s="2">
         <v>16502</v>
@@ -3643,33 +3641,33 @@
         <v>9</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F45" s="2">
         <v>1924</v>
@@ -3705,33 +3703,33 @@
         <v>1</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T45" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F46" s="2">
         <v>21760</v>
@@ -3767,33 +3765,33 @@
         <v>10</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="47">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F47" s="2">
         <v>1321</v>
@@ -3829,33 +3827,33 @@
         <v>18</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R47" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T47" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F48" s="2">
         <v>12655</v>
@@ -3891,33 +3889,33 @@
         <v>2</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T48" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F49" s="2">
         <v>1362</v>
@@ -3953,33 +3951,33 @@
         <v>16</v>
       </c>
       <c r="Q49" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R49" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F50" s="2">
         <v>6803</v>
@@ -4015,33 +4013,33 @@
         <v>0</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R50" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S50" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F51" s="2">
         <v>58243</v>
@@ -4077,33 +4075,33 @@
         <v>6</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T51" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F52" s="2">
         <v>11500</v>
@@ -4139,33 +4137,33 @@
         <v>92</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R52" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T52" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F53" s="2">
         <v>24101</v>
@@ -4201,33 +4199,33 @@
         <v>8</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S53" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T53" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F54" s="2">
         <v>132333</v>
@@ -4263,33 +4261,33 @@
         <v>53</v>
       </c>
       <c r="Q54" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R54" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S54" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T54" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="55">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F55" s="2">
         <v>781</v>
@@ -4325,33 +4323,33 @@
         <v>4</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R55" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S55" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T55" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F56" s="2">
         <v>1955</v>
@@ -4387,33 +4385,33 @@
         <v>29</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R56" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T56" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="57">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F57" s="2">
         <v>187004</v>
@@ -4449,33 +4447,33 @@
         <v>47</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R57" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T57" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="58">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F58" s="2">
         <v>395</v>
@@ -4511,33 +4509,33 @@
         <v>0</v>
       </c>
       <c r="Q58" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R58" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T58" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="59">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F59" s="2">
         <v>0</v>
@@ -4573,33 +4571,33 @@
         <v>0</v>
       </c>
       <c r="Q59" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R59" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T59" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="60">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F60" s="2">
         <v>0</v>
@@ -4635,33 +4633,33 @@
         <v>0</v>
       </c>
       <c r="Q60" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T60" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="61">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F61" s="2">
         <v>0</v>
@@ -4697,33 +4695,33 @@
         <v>0</v>
       </c>
       <c r="Q61" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R61" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F62" s="2">
         <v>0</v>
@@ -4759,33 +4757,33 @@
         <v>0</v>
       </c>
       <c r="Q62" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R62" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T62" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="63">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F63" s="2">
         <v>0</v>
@@ -4821,33 +4819,33 @@
         <v>0</v>
       </c>
       <c r="Q63" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R63" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T63" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="64">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F64" s="2">
         <v>0</v>
@@ -4883,33 +4881,33 @@
         <v>0</v>
       </c>
       <c r="Q64" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R64" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T64" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="65">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F65" s="2">
         <v>0</v>
@@ -4945,33 +4943,33 @@
         <v>0</v>
       </c>
       <c r="Q65" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R65" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T65" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="66">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F66" s="2">
         <v>0</v>
@@ -5007,33 +5005,33 @@
         <v>0</v>
       </c>
       <c r="Q66" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R66" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T66" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="67">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F67" s="2">
         <v>0</v>
@@ -5069,33 +5067,33 @@
         <v>0</v>
       </c>
       <c r="Q67" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R67" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S67" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T67" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="68">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F68" s="2">
         <v>0</v>
@@ -5131,33 +5129,33 @@
         <v>0</v>
       </c>
       <c r="Q68" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R68" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="69">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F69" s="2">
         <v>0</v>
@@ -5193,33 +5191,33 @@
         <v>0</v>
       </c>
       <c r="Q69" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R69" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S69" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T69" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="70">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F70" s="2">
         <v>0</v>
@@ -5255,33 +5253,33 @@
         <v>0</v>
       </c>
       <c r="Q70" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R70" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S70" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T70" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="71">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F71" s="2">
         <v>0</v>
@@ -5317,33 +5315,33 @@
         <v>0</v>
       </c>
       <c r="Q71" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R71" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S71" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T71" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="72">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F72" s="2">
         <v>0</v>
@@ -5379,33 +5377,33 @@
         <v>0</v>
       </c>
       <c r="Q72" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R72" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S72" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T72" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="73">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F73" s="2">
         <v>0</v>
@@ -5441,33 +5439,33 @@
         <v>0</v>
       </c>
       <c r="Q73" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R73" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S73" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T73" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="74">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F74" s="2">
         <v>0</v>
@@ -5503,33 +5501,33 @@
         <v>0</v>
       </c>
       <c r="Q74" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R74" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S74" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T74" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="75">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F75" s="2">
         <v>0</v>
@@ -5565,33 +5563,33 @@
         <v>0</v>
       </c>
       <c r="Q75" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R75" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S75" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T75" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="76">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F76" s="2">
         <v>0</v>
@@ -5627,33 +5625,33 @@
         <v>0</v>
       </c>
       <c r="Q76" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R76" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S76" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T76" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="77">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F77" s="2">
         <v>0</v>
@@ -5689,33 +5687,33 @@
         <v>0</v>
       </c>
       <c r="Q77" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R77" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S77" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T77" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="78">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F78" s="2">
         <v>0</v>
@@ -5751,33 +5749,33 @@
         <v>0</v>
       </c>
       <c r="Q78" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R78" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S78" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T78" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="79">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F79" s="2">
         <v>0</v>
@@ -5813,33 +5811,33 @@
         <v>0</v>
       </c>
       <c r="Q79" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R79" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S79" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T79" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="80">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F80" s="2">
         <v>0</v>
@@ -5875,33 +5873,33 @@
         <v>0</v>
       </c>
       <c r="Q80" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R80" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S80" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T80" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="81">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F81" s="2">
         <v>0</v>
@@ -5937,33 +5935,33 @@
         <v>0</v>
       </c>
       <c r="Q81" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R81" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S81" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T81" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="82">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F82" s="2">
         <v>0</v>
@@ -5999,33 +5997,33 @@
         <v>0</v>
       </c>
       <c r="Q82" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R82" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S82" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T82" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="83">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F83" s="2">
         <v>0</v>
@@ -6061,33 +6059,33 @@
         <v>0</v>
       </c>
       <c r="Q83" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R83" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S83" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T83" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="84">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F84" s="2">
         <v>0</v>
@@ -6123,33 +6121,33 @@
         <v>0</v>
       </c>
       <c r="Q84" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R84" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S84" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T84" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="85">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F85" s="2">
         <v>0</v>
@@ -6185,33 +6183,33 @@
         <v>0</v>
       </c>
       <c r="Q85" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R85" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S85" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T85" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="86">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F86" s="2">
         <v>0</v>
@@ -6247,33 +6245,33 @@
         <v>0</v>
       </c>
       <c r="Q86" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R86" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S86" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T86" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="87">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F87" s="2">
         <v>0</v>
@@ -6309,33 +6307,33 @@
         <v>0</v>
       </c>
       <c r="Q87" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R87" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S87" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T87" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="88">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F88" s="2">
         <v>0</v>
@@ -6371,33 +6369,33 @@
         <v>0</v>
       </c>
       <c r="Q88" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R88" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S88" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T88" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="89">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F89" s="2">
         <v>0</v>
@@ -6433,33 +6431,33 @@
         <v>0</v>
       </c>
       <c r="Q89" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R89" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S89" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T89" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="90">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F90" s="2">
         <v>0</v>
@@ -6495,33 +6493,33 @@
         <v>0</v>
       </c>
       <c r="Q90" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R90" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S90" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T90" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="91">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F91" s="2">
         <v>0</v>
@@ -6557,33 +6555,33 @@
         <v>0</v>
       </c>
       <c r="Q91" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R91" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S91" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T91" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="92">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F92" s="2">
         <v>0</v>
@@ -6619,33 +6617,33 @@
         <v>0</v>
       </c>
       <c r="Q92" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R92" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S92" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T92" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="93">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>65</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F93" s="2">
         <v>1498</v>
@@ -6681,33 +6679,33 @@
         <v>50</v>
       </c>
       <c r="Q93" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R93" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S93" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T93" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="94">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F94" s="2">
         <v>0</v>
@@ -6743,33 +6741,33 @@
         <v>0</v>
       </c>
       <c r="Q94" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R94" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S94" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T94" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="95">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F95" s="2">
         <v>0</v>
@@ -6805,33 +6803,33 @@
         <v>0</v>
       </c>
       <c r="Q95" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R95" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S95" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T95" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="96">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F96" s="2">
         <v>0</v>
@@ -6867,33 +6865,33 @@
         <v>0</v>
       </c>
       <c r="Q96" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R96" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S96" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T96" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="97">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F97" s="2">
         <v>0</v>
@@ -6929,33 +6927,33 @@
         <v>0</v>
       </c>
       <c r="Q97" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R97" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S97" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T97" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="98">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>65</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F98" s="2">
         <v>0</v>
@@ -6991,81 +6989,20 @@
         <v>0</v>
       </c>
       <c r="Q98" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R98" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S98" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T98" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F99" s="2">
-        <v>731609</v>
-      </c>
-      <c r="G99" s="2">
-        <v>2008384</v>
-      </c>
-      <c r="H99" s="2">
-        <v>1992409</v>
-      </c>
-      <c r="I99" s="2">
-        <v>1235116</v>
-      </c>
-      <c r="J99" s="2">
-        <v>508712</v>
-      </c>
-      <c r="K99" s="2">
-        <v>7896</v>
-      </c>
-      <c r="L99" s="2">
-        <v>217</v>
-      </c>
-      <c r="M99" s="2">
-        <v>146</v>
-      </c>
-      <c r="N99" s="2">
-        <v>4229</v>
-      </c>
-      <c r="O99" s="2">
-        <v>4526</v>
-      </c>
-      <c r="P99" s="2">
-        <v>1028</v>
-      </c>
-      <c r="Q99" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="R99" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="S99" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="T99" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/June.xlsx
+++ b/data/June.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D6C5727-9839-4DAD-B75C-59F90CE4FC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,31 +14,34 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>ผู้สร้าง</author>
+    <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
+            <rFont val="Arial"/>
+            <color/>
             <sz val="12"/>
-            <rFont val="Arial"/>
           </rPr>
-          <t>This is a reach-based metric. Reach-based metrics are de-duplicated metrics so you might see different numbers based on the level at which you are viewing data.</t>
+          <t xml:space="preserve">This is a reach-based metric. Reach-based metrics are de-duplicated metrics so you might see different numbers based on the level at which you are viewing data.</t>
         </r>
         <r>
           <rPr>
+            <rFont val="Arial"/>
+            <color/>
             <sz val="12"/>
-            <rFont val="Arial"/>
           </rPr>
           <t xml:space="preserve">     </t>
         </r>
         <r>
           <rPr>
+            <rFont val="Arial"/>
+            <color/>
             <sz val="12"/>
-            <rFont val="Arial"/>
           </rPr>
           <t xml:space="preserve">     </t>
         </r>
@@ -50,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
   <si>
     <t>Ad name</t>
   </si>
@@ -256,13 +258,13 @@
     <t>หมดกองนี้ ลูกค้ารับไปเลย 23,XXX บาท</t>
   </si>
   <si>
+    <t>Total of 97 results</t>
+  </si>
+  <si>
     <t>Primary status</t>
   </si>
   <si>
-    <t>Not delivering</t>
-  </si>
-  <si>
-    <t>Active</t>
+    <t>Ended</t>
   </si>
   <si>
     <t>Paused</t>
@@ -274,22 +276,22 @@
     <t>Secondary status</t>
   </si>
   <si>
-    <t>Out of campaign budget</t>
-  </si>
-  <si>
-    <t>--</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ; Out of campaign budget</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ; Out of campaign budget; Review not approved</t>
-  </si>
-  <si>
-    <t>Review not approved</t>
+    <t>Ad completed; Out of campaign budget</t>
+  </si>
+  <si>
+    <t>Ad completed</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ; Ad completed; Out of campaign budget</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ; Ad completed</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ; Ad completed; Out of campaign budget; Review not approved</t>
+  </si>
+  <si>
+    <t>Ad completed; Out of campaign budget; Review not approved</t>
   </si>
   <si>
     <t>Campaign name</t>
@@ -388,25 +390,25 @@
     <t>216.87</t>
   </si>
   <si>
-    <t>3631.96</t>
-  </si>
-  <si>
-    <t>24.33</t>
-  </si>
-  <si>
-    <t>866.26</t>
-  </si>
-  <si>
-    <t>221.48</t>
-  </si>
-  <si>
-    <t>612.52</t>
-  </si>
-  <si>
-    <t>10.13</t>
-  </si>
-  <si>
-    <t>2017.03</t>
+    <t>4142.88</t>
+  </si>
+  <si>
+    <t>27.57</t>
+  </si>
+  <si>
+    <t>934.47</t>
+  </si>
+  <si>
+    <t>263.03</t>
+  </si>
+  <si>
+    <t>648.08</t>
+  </si>
+  <si>
+    <t>12.59</t>
+  </si>
+  <si>
+    <t>2132.58</t>
   </si>
   <si>
     <t>8.61</t>
@@ -418,58 +420,61 @@
     <t>1200.00</t>
   </si>
   <si>
-    <t>1501.06</t>
-  </si>
-  <si>
-    <t>1159.23</t>
-  </si>
-  <si>
-    <t>1099.10</t>
-  </si>
-  <si>
-    <t>304.11</t>
-  </si>
-  <si>
-    <t>317.61</t>
-  </si>
-  <si>
-    <t>0.32</t>
-  </si>
-  <si>
-    <t>571.03</t>
-  </si>
-  <si>
-    <t>930.57</t>
-  </si>
-  <si>
-    <t>498.77</t>
+    <t>1600.00</t>
+  </si>
+  <si>
+    <t>1237.71</t>
+  </si>
+  <si>
+    <t>1174.50</t>
+  </si>
+  <si>
+    <t>331.44</t>
+  </si>
+  <si>
+    <t>335.04</t>
+  </si>
+  <si>
+    <t>0.37</t>
+  </si>
+  <si>
+    <t>612.76</t>
+  </si>
+  <si>
+    <t>986.73</t>
+  </si>
+  <si>
+    <t>530.19</t>
   </si>
   <si>
     <t>4747.76</t>
   </si>
   <si>
-    <t>1523.37</t>
-  </si>
-  <si>
-    <t>211.92</t>
-  </si>
-  <si>
-    <t>440.78</t>
-  </si>
-  <si>
-    <t>1155.35</t>
-  </si>
-  <si>
-    <t>152.62</t>
-  </si>
-  <si>
-    <t>911.71</t>
-  </si>
-  <si>
-    <t>6483.83</t>
-  </si>
-  <si>
-    <t>2706.85</t>
+    <t>24.49</t>
+  </si>
+  <si>
+    <t>1599.96</t>
+  </si>
+  <si>
+    <t>218.52</t>
+  </si>
+  <si>
+    <t>446.99</t>
+  </si>
+  <si>
+    <t>1177.07</t>
+  </si>
+  <si>
+    <t>159.90</t>
+  </si>
+  <si>
+    <t>939.33</t>
+  </si>
+  <si>
+    <t>6500.00</t>
+  </si>
+  <si>
+    <t>2850.29</t>
   </si>
   <si>
     <t>15.74</t>
@@ -478,37 +483,31 @@
     <t>368.95</t>
   </si>
   <si>
-    <t>6330.88</t>
-  </si>
-  <si>
-    <t>3142.56</t>
-  </si>
-  <si>
-    <t>696.72</t>
-  </si>
-  <si>
-    <t>55.49</t>
-  </si>
-  <si>
-    <t>840.92</t>
-  </si>
-  <si>
-    <t>361.60</t>
-  </si>
-  <si>
-    <t>181.17</t>
-  </si>
-  <si>
-    <t>1339.56</t>
-  </si>
-  <si>
-    <t>6388.13</t>
-  </si>
-  <si>
-    <t>619.61</t>
-  </si>
-  <si>
-    <t>3613.87</t>
+    <t>3285.76</t>
+  </si>
+  <si>
+    <t>768.12</t>
+  </si>
+  <si>
+    <t>57.22</t>
+  </si>
+  <si>
+    <t>888.25</t>
+  </si>
+  <si>
+    <t>361.67</t>
+  </si>
+  <si>
+    <t>181.60</t>
+  </si>
+  <si>
+    <t>1418.16</t>
+  </si>
+  <si>
+    <t>659.37</t>
+  </si>
+  <si>
+    <t>3809.97</t>
   </si>
   <si>
     <t>417.84</t>
@@ -517,7 +516,7 @@
     <t>1697.87</t>
   </si>
   <si>
-    <t>5769.63</t>
+    <t>5801.08</t>
   </si>
   <si>
     <t>4.22</t>
@@ -527,6 +526,9 @@
   </si>
   <si>
     <t>2532.61</t>
+  </si>
+  <si>
+    <t>81737.65</t>
   </si>
   <si>
     <t>Reach</t>
@@ -586,8 +588,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -595,19 +597,17 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
       <sz val="12"/>
+      <color/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
+      <color/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -645,140 +645,136 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+      <alignment/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="44546A"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="ED7D31"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="FFC000"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4472C4"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="70AD47"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0563C1"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="954F72"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
+<theme xmlns="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+  <themeElements>
+    <clrScheme name="Office">
+      <dk1>
+        <sysClr val="windowText" lastClr="000000"/>
+      </dk1>
+      <lt1>
+        <sysClr val="window" lastClr="FFFFFF"/>
+      </lt1>
+      <dk2>
+        <srgbClr val="44546A"/>
+      </dk2>
+      <lt2>
+        <srgbClr val="E7E6E6"/>
+      </lt2>
+      <accent1>
+        <srgbClr val="5B9BD5"/>
+      </accent1>
+      <accent2>
+        <srgbClr val="ED7D31"/>
+      </accent2>
+      <accent3>
+        <srgbClr val="A5A5A5"/>
+      </accent3>
+      <accent4>
+        <srgbClr val="FFC000"/>
+      </accent4>
+      <accent5>
+        <srgbClr val="4472C4"/>
+      </accent5>
+      <accent6>
+        <srgbClr val="70AD47"/>
+      </accent6>
+      <hlink>
+        <srgbClr val="0563C1"/>
+      </hlink>
+      <folHlink>
+        <srgbClr val="954F72"/>
+      </folHlink>
+    </clrScheme>
+    <fontScheme name="Office">
+      <majorFont>
+        <latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <ea typeface=""/>
+        <cs typeface=""/>
+        <font script="Jpan" typeface="游ゴシック Light"/>
+        <font script="Hang" typeface="맑은 고딕"/>
+        <font script="Hans" typeface="等线 Light"/>
+        <font script="Hant" typeface="新細明體"/>
+        <font script="Arab" typeface="Times New Roman"/>
+        <font script="Hebr" typeface="Times New Roman"/>
+        <font script="Thai" typeface="Tahoma"/>
+        <font script="Ethi" typeface="Nyala"/>
+        <font script="Beng" typeface="Vrinda"/>
+        <font script="Gujr" typeface="Shruti"/>
+        <font script="Khmr" typeface="MoolBoran"/>
+        <font script="Knda" typeface="Tunga"/>
+        <font script="Guru" typeface="Raavi"/>
+        <font script="Cans" typeface="Euphemia"/>
+        <font script="Cher" typeface="Plantagenet Cherokee"/>
+        <font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <font script="Tibt" typeface="Microsoft Himalaya"/>
+        <font script="Thaa" typeface="MV Boli"/>
+        <font script="Deva" typeface="Mangal"/>
+        <font script="Telu" typeface="Gautami"/>
+        <font script="Taml" typeface="Latha"/>
+        <font script="Syrc" typeface="Estrangelo Edessa"/>
+        <font script="Orya" typeface="Kalinga"/>
+        <font script="Mlym" typeface="Kartika"/>
+        <font script="Laoo" typeface="DokChampa"/>
+        <font script="Sinh" typeface="Iskoola Pota"/>
+        <font script="Mong" typeface="Mongolian Baiti"/>
+        <font script="Viet" typeface="Times New Roman"/>
+        <font script="Uigh" typeface="Microsoft Uighur"/>
+        <font script="Geor" typeface="Sylfaen"/>
+      </majorFont>
+      <minorFont>
+        <latin typeface="Calibri" panose="020F0502020204030204"/>
+        <ea typeface=""/>
+        <cs typeface=""/>
+        <font script="Jpan" typeface="游ゴシック"/>
+        <font script="Hang" typeface="맑은 고딕"/>
+        <font script="Hans" typeface="等线"/>
+        <font script="Hant" typeface="新細明體"/>
+        <font script="Arab" typeface="Arial"/>
+        <font script="Hebr" typeface="Arial"/>
+        <font script="Thai" typeface="Tahoma"/>
+        <font script="Ethi" typeface="Nyala"/>
+        <font script="Beng" typeface="Vrinda"/>
+        <font script="Gujr" typeface="Shruti"/>
+        <font script="Khmr" typeface="DaunPenh"/>
+        <font script="Knda" typeface="Tunga"/>
+        <font script="Guru" typeface="Raavi"/>
+        <font script="Cans" typeface="Euphemia"/>
+        <font script="Cher" typeface="Plantagenet Cherokee"/>
+        <font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <font script="Tibt" typeface="Microsoft Himalaya"/>
+        <font script="Thaa" typeface="MV Boli"/>
+        <font script="Deva" typeface="Mangal"/>
+        <font script="Telu" typeface="Gautami"/>
+        <font script="Taml" typeface="Latha"/>
+        <font script="Syrc" typeface="Estrangelo Edessa"/>
+        <font script="Orya" typeface="Kalinga"/>
+        <font script="Mlym" typeface="Kartika"/>
+        <font script="Laoo" typeface="DokChampa"/>
+        <font script="Sinh" typeface="Iskoola Pota"/>
+        <font script="Mong" typeface="Mongolian Baiti"/>
+        <font script="Viet" typeface="Arial"/>
+        <font script="Uigh" typeface="Microsoft Uighur"/>
+        <font script="Geor" typeface="Sylfaen"/>
+      </minorFont>
+    </fontScheme>
+    <fmtScheme name="Office">
+      <fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -834,8 +830,8 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
+      </fillStyleLst>
+      <lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -857,8 +853,8 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
+      </lnStyleLst>
+      <effectStyleLst>
         <a:effectStyle>
           <a:effectLst/>
         </a:effectStyle>
@@ -874,8 +870,8 @@
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
+      </effectStyleLst>
+      <bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -912,25 +908,25 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
+      </bgFillStyleLst>
+    </fmtScheme>
+  </themeElements>
+  <objectDefaults/>
+  <extraClrSchemeLst/>
+</theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T98"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>73</v>
@@ -987,12 +983,12 @@
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>74</v>
@@ -1049,12 +1045,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>74</v>
@@ -1111,7 +1107,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1119,7 +1115,7 @@
         <v>70</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>82</v>
@@ -1128,22 +1124,22 @@
         <v>112</v>
       </c>
       <c r="F4" s="2">
-        <v>144062</v>
+        <v>160854</v>
       </c>
       <c r="G4" s="2">
-        <v>184801</v>
+        <v>209679</v>
       </c>
       <c r="H4" s="2">
-        <v>183652</v>
+        <v>208369</v>
       </c>
       <c r="I4" s="2">
-        <v>120352</v>
+        <v>135916</v>
       </c>
       <c r="J4" s="2">
-        <v>52177</v>
+        <v>58669</v>
       </c>
       <c r="K4" s="2">
-        <v>252</v>
+        <v>311</v>
       </c>
       <c r="L4" s="2">
         <v>2</v>
@@ -1152,13 +1148,13 @@
         <v>2</v>
       </c>
       <c r="N4" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O4" s="2">
-        <v>325</v>
+        <v>362</v>
       </c>
       <c r="P4" s="2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>171</v>
@@ -1173,7 +1169,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -1181,7 +1177,7 @@
         <v>70</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>82</v>
@@ -1190,22 +1186,22 @@
         <v>113</v>
       </c>
       <c r="F5" s="2">
-        <v>1564</v>
+        <v>1683</v>
       </c>
       <c r="G5" s="2">
-        <v>1634</v>
+        <v>1780</v>
       </c>
       <c r="H5" s="2">
-        <v>1627</v>
+        <v>1773</v>
       </c>
       <c r="I5" s="2">
-        <v>1105</v>
+        <v>1205</v>
       </c>
       <c r="J5" s="2">
-        <v>336</v>
+        <v>377</v>
       </c>
       <c r="K5" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L5" s="2">
         <v>0</v>
@@ -1217,7 +1213,7 @@
         <v>1</v>
       </c>
       <c r="O5" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P5" s="2">
         <v>1</v>
@@ -1235,7 +1231,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -1252,22 +1248,22 @@
         <v>114</v>
       </c>
       <c r="F6" s="2">
-        <v>39669</v>
+        <v>41778</v>
       </c>
       <c r="G6" s="2">
-        <v>54167</v>
+        <v>57793</v>
       </c>
       <c r="H6" s="2">
-        <v>53802</v>
+        <v>57408</v>
       </c>
       <c r="I6" s="2">
-        <v>32830</v>
+        <v>34992</v>
       </c>
       <c r="J6" s="2">
-        <v>15034</v>
+        <v>15967</v>
       </c>
       <c r="K6" s="2">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="L6" s="2">
         <v>0</v>
@@ -1276,13 +1272,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O6" s="2">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="P6" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>171</v>
@@ -1297,7 +1293,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -1305,7 +1301,7 @@
         <v>70</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>84</v>
@@ -1314,19 +1310,19 @@
         <v>115</v>
       </c>
       <c r="F7" s="2">
-        <v>7287</v>
+        <v>8097</v>
       </c>
       <c r="G7" s="2">
-        <v>9357</v>
+        <v>10637</v>
       </c>
       <c r="H7" s="2">
-        <v>9303</v>
+        <v>10575</v>
       </c>
       <c r="I7" s="2">
-        <v>5997</v>
+        <v>6822</v>
       </c>
       <c r="J7" s="2">
-        <v>2134</v>
+        <v>2439</v>
       </c>
       <c r="K7" s="2">
         <v>14</v>
@@ -1338,10 +1334,10 @@
         <v>0</v>
       </c>
       <c r="N7" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O7" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P7" s="2">
         <v>2</v>
@@ -1359,7 +1355,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -1367,7 +1363,7 @@
         <v>70</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>85</v>
@@ -1376,22 +1372,22 @@
         <v>116</v>
       </c>
       <c r="F8" s="2">
-        <v>19454</v>
+        <v>19886</v>
       </c>
       <c r="G8" s="2">
-        <v>28193</v>
+        <v>29046</v>
       </c>
       <c r="H8" s="2">
-        <v>27983</v>
+        <v>28831</v>
       </c>
       <c r="I8" s="2">
-        <v>13069</v>
+        <v>13448</v>
       </c>
       <c r="J8" s="2">
-        <v>5011</v>
+        <v>5167</v>
       </c>
       <c r="K8" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L8" s="2">
         <v>0</v>
@@ -1421,7 +1417,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -1429,7 +1425,7 @@
         <v>70</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>85</v>
@@ -1438,19 +1434,19 @@
         <v>117</v>
       </c>
       <c r="F9" s="2">
-        <v>769</v>
+        <v>782</v>
       </c>
       <c r="G9" s="2">
-        <v>831</v>
+        <v>851</v>
       </c>
       <c r="H9" s="2">
-        <v>828</v>
+        <v>848</v>
       </c>
       <c r="I9" s="2">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="J9" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="K9" s="2">
         <v>1</v>
@@ -1483,7 +1479,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
@@ -1500,22 +1496,22 @@
         <v>118</v>
       </c>
       <c r="F10" s="2">
-        <v>55903</v>
+        <v>58078</v>
       </c>
       <c r="G10" s="2">
-        <v>99747</v>
+        <v>105299</v>
       </c>
       <c r="H10" s="2">
-        <v>99264</v>
+        <v>104790</v>
       </c>
       <c r="I10" s="2">
-        <v>63948</v>
+        <v>67354</v>
       </c>
       <c r="J10" s="2">
-        <v>30043</v>
+        <v>31489</v>
       </c>
       <c r="K10" s="2">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="L10" s="2">
         <v>0</v>
@@ -1527,10 +1523,10 @@
         <v>21</v>
       </c>
       <c r="O10" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="P10" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>171</v>
@@ -1545,12 +1541,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>74</v>
@@ -1607,12 +1603,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>74</v>
@@ -1669,12 +1665,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>74</v>
@@ -1731,7 +1727,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
@@ -1739,7 +1735,7 @@
         <v>70</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>89</v>
@@ -1748,22 +1744,22 @@
         <v>122</v>
       </c>
       <c r="F14" s="2">
-        <v>46733</v>
+        <v>48515</v>
       </c>
       <c r="G14" s="2">
-        <v>78489</v>
+        <v>83160</v>
       </c>
       <c r="H14" s="2">
-        <v>77782</v>
+        <v>82391</v>
       </c>
       <c r="I14" s="2">
-        <v>41470</v>
+        <v>43745</v>
       </c>
       <c r="J14" s="2">
-        <v>13571</v>
+        <v>14320</v>
       </c>
       <c r="K14" s="2">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="L14" s="2">
         <v>0</v>
@@ -1772,13 +1768,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O14" s="2">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="P14" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>171</v>
@@ -1793,7 +1789,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15">
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
@@ -1810,37 +1806,37 @@
         <v>123</v>
       </c>
       <c r="F15" s="2">
-        <v>62804</v>
+        <v>65866</v>
       </c>
       <c r="G15" s="2">
-        <v>82624</v>
+        <v>87537</v>
       </c>
       <c r="H15" s="2">
-        <v>82078</v>
+        <v>86957</v>
       </c>
       <c r="I15" s="2">
-        <v>64408</v>
+        <v>68092</v>
       </c>
       <c r="J15" s="2">
-        <v>28011</v>
+        <v>29437</v>
       </c>
       <c r="K15" s="2">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="L15" s="2">
         <v>1</v>
       </c>
       <c r="M15" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N15" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="O15" s="2">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="P15" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Q15" s="2" t="s">
         <v>171</v>
@@ -1855,12 +1851,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16">
       <c r="A16" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>74</v>
@@ -1917,7 +1913,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17">
       <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
@@ -1925,7 +1921,7 @@
         <v>70</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>92</v>
@@ -1934,19 +1930,19 @@
         <v>124</v>
       </c>
       <c r="F17" s="2">
-        <v>39678</v>
+        <v>41343</v>
       </c>
       <c r="G17" s="2">
-        <v>55209</v>
+        <v>58425</v>
       </c>
       <c r="H17" s="2">
-        <v>54846</v>
+        <v>58041</v>
       </c>
       <c r="I17" s="2">
-        <v>34020</v>
+        <v>35966</v>
       </c>
       <c r="J17" s="2">
-        <v>11378</v>
+        <v>11991</v>
       </c>
       <c r="K17" s="2">
         <v>93</v>
@@ -1961,10 +1957,10 @@
         <v>7</v>
       </c>
       <c r="O17" s="2">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="P17" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>171</v>
@@ -1979,7 +1975,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18">
       <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
@@ -1987,7 +1983,7 @@
         <v>70</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>92</v>
@@ -1996,22 +1992,22 @@
         <v>125</v>
       </c>
       <c r="F18" s="2">
-        <v>12714</v>
+        <v>13674</v>
       </c>
       <c r="G18" s="2">
-        <v>16385</v>
+        <v>17792</v>
       </c>
       <c r="H18" s="2">
-        <v>16251</v>
+        <v>17639</v>
       </c>
       <c r="I18" s="2">
-        <v>9076</v>
+        <v>9767</v>
       </c>
       <c r="J18" s="2">
-        <v>3227</v>
+        <v>3468</v>
       </c>
       <c r="K18" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L18" s="2">
         <v>0</v>
@@ -2023,7 +2019,7 @@
         <v>4</v>
       </c>
       <c r="O18" s="2">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="P18" s="2">
         <v>3</v>
@@ -2041,7 +2037,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19">
       <c r="A19" s="2" t="s">
         <v>15</v>
       </c>
@@ -2049,7 +2045,7 @@
         <v>70</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>92</v>
@@ -2058,22 +2054,22 @@
         <v>126</v>
       </c>
       <c r="F19" s="2">
-        <v>12162</v>
+        <v>12677</v>
       </c>
       <c r="G19" s="2">
-        <v>14838</v>
+        <v>15720</v>
       </c>
       <c r="H19" s="2">
-        <v>14737</v>
+        <v>15613</v>
       </c>
       <c r="I19" s="2">
-        <v>8086</v>
+        <v>8557</v>
       </c>
       <c r="J19" s="2">
-        <v>2801</v>
+        <v>2945</v>
       </c>
       <c r="K19" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L19" s="2">
         <v>0</v>
@@ -2085,10 +2081,10 @@
         <v>1</v>
       </c>
       <c r="O19" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P19" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q19" s="2" t="s">
         <v>171</v>
@@ -2103,7 +2099,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20">
       <c r="A20" s="2" t="s">
         <v>16</v>
       </c>
@@ -2111,7 +2107,7 @@
         <v>70</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>93</v>
@@ -2120,19 +2116,19 @@
         <v>127</v>
       </c>
       <c r="F20" s="2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G20" s="2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H20" s="2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I20" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J20" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K20" s="2">
         <v>0</v>
@@ -2165,12 +2161,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21">
       <c r="A21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>74</v>
@@ -2227,7 +2223,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22">
       <c r="A22" s="2" t="s">
         <v>18</v>
       </c>
@@ -2244,22 +2240,22 @@
         <v>128</v>
       </c>
       <c r="F22" s="2">
-        <v>28706</v>
+        <v>30399</v>
       </c>
       <c r="G22" s="2">
-        <v>36847</v>
+        <v>39568</v>
       </c>
       <c r="H22" s="2">
-        <v>36610</v>
+        <v>39311</v>
       </c>
       <c r="I22" s="2">
-        <v>24530</v>
+        <v>26212</v>
       </c>
       <c r="J22" s="2">
-        <v>10077</v>
+        <v>10729</v>
       </c>
       <c r="K22" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="L22" s="2">
         <v>1</v>
@@ -2268,10 +2264,10 @@
         <v>0</v>
       </c>
       <c r="N22" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O22" s="2">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="P22" s="2">
         <v>9</v>
@@ -2289,7 +2285,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23">
       <c r="A23" s="2" t="s">
         <v>19</v>
       </c>
@@ -2306,22 +2302,22 @@
         <v>129</v>
       </c>
       <c r="F23" s="2">
-        <v>42440</v>
+        <v>44346</v>
       </c>
       <c r="G23" s="2">
-        <v>52589</v>
+        <v>55786</v>
       </c>
       <c r="H23" s="2">
-        <v>52310</v>
+        <v>55493</v>
       </c>
       <c r="I23" s="2">
-        <v>34299</v>
+        <v>36207</v>
       </c>
       <c r="J23" s="2">
-        <v>15297</v>
+        <v>16095</v>
       </c>
       <c r="K23" s="2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L23" s="2">
         <v>0</v>
@@ -2333,10 +2329,10 @@
         <v>6</v>
       </c>
       <c r="O23" s="2">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="P23" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q23" s="2" t="s">
         <v>171</v>
@@ -2351,7 +2347,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24">
       <c r="A24" s="2" t="s">
         <v>20</v>
       </c>
@@ -2368,22 +2364,22 @@
         <v>130</v>
       </c>
       <c r="F24" s="2">
-        <v>23593</v>
+        <v>24977</v>
       </c>
       <c r="G24" s="2">
-        <v>31224</v>
+        <v>33121</v>
       </c>
       <c r="H24" s="2">
-        <v>31053</v>
+        <v>32932</v>
       </c>
       <c r="I24" s="2">
-        <v>23423</v>
+        <v>24639</v>
       </c>
       <c r="J24" s="2">
-        <v>9133</v>
+        <v>9551</v>
       </c>
       <c r="K24" s="2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="L24" s="2">
         <v>1</v>
@@ -2395,7 +2391,7 @@
         <v>4</v>
       </c>
       <c r="O24" s="2">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="P24" s="2">
         <v>3</v>
@@ -2413,12 +2409,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25">
       <c r="A25" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>74</v>
@@ -2454,7 +2450,7 @@
         <v>10</v>
       </c>
       <c r="N25" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O25" s="2">
         <v>48</v>
@@ -2475,7 +2471,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26">
       <c r="A26" s="2" t="s">
         <v>21</v>
       </c>
@@ -2483,28 +2479,28 @@
         <v>70</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>82</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="F26" s="2">
-        <v>1100</v>
+        <v>1108</v>
       </c>
       <c r="G26" s="2">
-        <v>1337</v>
+        <v>1347</v>
       </c>
       <c r="H26" s="2">
-        <v>1324</v>
+        <v>1334</v>
       </c>
       <c r="I26" s="2">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="J26" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K26" s="2">
         <v>3</v>
@@ -2537,12 +2533,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27">
       <c r="A27" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>74</v>
@@ -2599,7 +2595,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28">
       <c r="A28" s="2" t="s">
         <v>23</v>
       </c>
@@ -2613,25 +2609,25 @@
         <v>98</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F28" s="2">
-        <v>74114</v>
+        <v>76578</v>
       </c>
       <c r="G28" s="2">
-        <v>107921</v>
+        <v>112848</v>
       </c>
       <c r="H28" s="2">
-        <v>107331</v>
+        <v>112233</v>
       </c>
       <c r="I28" s="2">
-        <v>76941</v>
+        <v>80251</v>
       </c>
       <c r="J28" s="2">
-        <v>38026</v>
+        <v>39493</v>
       </c>
       <c r="K28" s="2">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="L28" s="2">
         <v>0</v>
@@ -2640,13 +2636,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O28" s="2">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="P28" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q28" s="2" t="s">
         <v>171</v>
@@ -2661,12 +2657,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29">
       <c r="A29" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>74</v>
@@ -2723,7 +2719,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30">
       <c r="A30" s="2" t="s">
         <v>24</v>
       </c>
@@ -2737,25 +2733,25 @@
         <v>83</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F30" s="2">
-        <v>7734</v>
+        <v>7842</v>
       </c>
       <c r="G30" s="2">
-        <v>10655</v>
+        <v>10973</v>
       </c>
       <c r="H30" s="2">
-        <v>10562</v>
+        <v>10878</v>
       </c>
       <c r="I30" s="2">
-        <v>6678</v>
+        <v>6870</v>
       </c>
       <c r="J30" s="2">
-        <v>3074</v>
+        <v>3176</v>
       </c>
       <c r="K30" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L30" s="2">
         <v>0</v>
@@ -2767,7 +2763,7 @@
         <v>2</v>
       </c>
       <c r="O30" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P30" s="2">
         <v>6</v>
@@ -2785,7 +2781,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31">
       <c r="A31" s="2" t="s">
         <v>25</v>
       </c>
@@ -2799,25 +2795,25 @@
         <v>83</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F31" s="2">
-        <v>13338</v>
+        <v>13459</v>
       </c>
       <c r="G31" s="2">
-        <v>19104</v>
+        <v>19429</v>
       </c>
       <c r="H31" s="2">
-        <v>18993</v>
+        <v>19317</v>
       </c>
       <c r="I31" s="2">
-        <v>14043</v>
+        <v>14304</v>
       </c>
       <c r="J31" s="2">
-        <v>5894</v>
+        <v>5985</v>
       </c>
       <c r="K31" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L31" s="2">
         <v>0</v>
@@ -2829,7 +2825,7 @@
         <v>7</v>
       </c>
       <c r="O31" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P31" s="2">
         <v>2</v>
@@ -2847,12 +2843,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32">
       <c r="A32" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>74</v>
@@ -2909,7 +2905,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33">
       <c r="A33" s="2" t="s">
         <v>26</v>
       </c>
@@ -2917,28 +2913,28 @@
         <v>70</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>84</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F33" s="2">
-        <v>35072</v>
+        <v>35613</v>
       </c>
       <c r="G33" s="2">
-        <v>53125</v>
+        <v>54211</v>
       </c>
       <c r="H33" s="2">
-        <v>52669</v>
+        <v>53742</v>
       </c>
       <c r="I33" s="2">
-        <v>29095</v>
+        <v>29661</v>
       </c>
       <c r="J33" s="2">
-        <v>10219</v>
+        <v>10400</v>
       </c>
       <c r="K33" s="2">
         <v>74</v>
@@ -2953,7 +2949,7 @@
         <v>10</v>
       </c>
       <c r="O33" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="P33" s="2">
         <v>8</v>
@@ -2971,7 +2967,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34">
       <c r="A34" s="2" t="s">
         <v>27</v>
       </c>
@@ -2979,28 +2975,28 @@
         <v>70</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>84</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F34" s="2">
-        <v>5710</v>
+        <v>5864</v>
       </c>
       <c r="G34" s="2">
-        <v>7181</v>
+        <v>7464</v>
       </c>
       <c r="H34" s="2">
-        <v>7141</v>
+        <v>7423</v>
       </c>
       <c r="I34" s="2">
-        <v>4329</v>
+        <v>4523</v>
       </c>
       <c r="J34" s="2">
-        <v>1109</v>
+        <v>1160</v>
       </c>
       <c r="K34" s="2">
         <v>6</v>
@@ -3015,7 +3011,7 @@
         <v>2</v>
       </c>
       <c r="O34" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P34" s="2">
         <v>0</v>
@@ -3033,12 +3029,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35">
       <c r="A35" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>74</v>
@@ -3095,7 +3091,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36">
       <c r="A36" s="2" t="s">
         <v>29</v>
       </c>
@@ -3103,31 +3099,31 @@
         <v>70</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>85</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F36" s="2">
-        <v>23506</v>
+        <v>23937</v>
       </c>
       <c r="G36" s="2">
-        <v>31084</v>
+        <v>31795</v>
       </c>
       <c r="H36" s="2">
-        <v>30789</v>
+        <v>31494</v>
       </c>
       <c r="I36" s="2">
-        <v>16383</v>
+        <v>16725</v>
       </c>
       <c r="J36" s="2">
-        <v>4777</v>
+        <v>4881</v>
       </c>
       <c r="K36" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L36" s="2">
         <v>0</v>
@@ -3136,10 +3132,10 @@
         <v>0</v>
       </c>
       <c r="N36" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O36" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P36" s="2">
         <v>3</v>
@@ -3157,7 +3153,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37">
       <c r="A37" s="2" t="s">
         <v>30</v>
       </c>
@@ -3165,31 +3161,31 @@
         <v>70</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>102</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F37" s="2">
-        <v>10626</v>
+        <v>10663</v>
       </c>
       <c r="G37" s="2">
-        <v>20035</v>
+        <v>20074</v>
       </c>
       <c r="H37" s="2">
-        <v>19337</v>
+        <v>19375</v>
       </c>
       <c r="I37" s="2">
-        <v>4452</v>
+        <v>4463</v>
       </c>
       <c r="J37" s="2">
-        <v>1281</v>
+        <v>1285</v>
       </c>
       <c r="K37" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="L37" s="2">
         <v>25</v>
@@ -3198,7 +3194,7 @@
         <v>19</v>
       </c>
       <c r="N37" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="O37" s="2">
         <v>86</v>
@@ -3219,7 +3215,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38">
       <c r="A38" s="2" t="s">
         <v>31</v>
       </c>
@@ -3233,25 +3229,25 @@
         <v>86</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F38" s="2">
-        <v>87218</v>
+        <v>91034</v>
       </c>
       <c r="G38" s="2">
-        <v>145755</v>
+        <v>155354</v>
       </c>
       <c r="H38" s="2">
-        <v>144559</v>
+        <v>154077</v>
       </c>
       <c r="I38" s="2">
-        <v>75827</v>
+        <v>80076</v>
       </c>
       <c r="J38" s="2">
-        <v>31325</v>
+        <v>32936</v>
       </c>
       <c r="K38" s="2">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="L38" s="2">
         <v>1</v>
@@ -3260,13 +3256,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O38" s="2">
-        <v>701</v>
+        <v>760</v>
       </c>
       <c r="P38" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q38" s="2" t="s">
         <v>171</v>
@@ -3281,7 +3277,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39">
       <c r="A39" s="2" t="s">
         <v>30</v>
       </c>
@@ -3295,7 +3291,7 @@
         <v>86</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F39" s="2">
         <v>480</v>
@@ -3343,12 +3339,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40">
       <c r="A40" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>74</v>
@@ -3405,12 +3401,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41">
       <c r="A41" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>74</v>
@@ -3419,7 +3415,7 @@
         <v>87</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F41" s="2">
         <v>7991</v>
@@ -3467,7 +3463,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42">
       <c r="A42" s="2" t="s">
         <v>34</v>
       </c>
@@ -3475,31 +3471,31 @@
         <v>70</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>104</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F42" s="2">
-        <v>15059</v>
+        <v>15380</v>
       </c>
       <c r="G42" s="2">
-        <v>29241</v>
+        <v>30150</v>
       </c>
       <c r="H42" s="2">
-        <v>28427</v>
+        <v>29314</v>
       </c>
       <c r="I42" s="2">
-        <v>8225</v>
+        <v>8483</v>
       </c>
       <c r="J42" s="2">
-        <v>2984</v>
+        <v>3074</v>
       </c>
       <c r="K42" s="2">
-        <v>739</v>
+        <v>763</v>
       </c>
       <c r="L42" s="2">
         <v>43</v>
@@ -3508,10 +3504,10 @@
         <v>24</v>
       </c>
       <c r="N42" s="2">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="O42" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="P42" s="2">
         <v>116</v>
@@ -3529,7 +3525,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43">
       <c r="A43" s="2" t="s">
         <v>34</v>
       </c>
@@ -3546,22 +3542,22 @@
         <v>143</v>
       </c>
       <c r="F43" s="2">
-        <v>66090</v>
+        <v>67764</v>
       </c>
       <c r="G43" s="2">
-        <v>116376</v>
+        <v>120852</v>
       </c>
       <c r="H43" s="2">
-        <v>115550</v>
+        <v>119978</v>
       </c>
       <c r="I43" s="2">
-        <v>57826</v>
+        <v>59965</v>
       </c>
       <c r="J43" s="2">
-        <v>24616</v>
+        <v>25481</v>
       </c>
       <c r="K43" s="2">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="L43" s="2">
         <v>0</v>
@@ -3570,13 +3566,13 @@
         <v>4</v>
       </c>
       <c r="N43" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O43" s="2">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="P43" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q43" s="2" t="s">
         <v>171</v>
@@ -3591,7 +3587,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44">
       <c r="A44" s="2" t="s">
         <v>35</v>
       </c>
@@ -3608,22 +3604,22 @@
         <v>144</v>
       </c>
       <c r="F44" s="2">
-        <v>16502</v>
+        <v>17704</v>
       </c>
       <c r="G44" s="2">
-        <v>29971</v>
+        <v>33068</v>
       </c>
       <c r="H44" s="2">
-        <v>29688</v>
+        <v>32755</v>
       </c>
       <c r="I44" s="2">
-        <v>12779</v>
+        <v>13954</v>
       </c>
       <c r="J44" s="2">
-        <v>5176</v>
+        <v>5616</v>
       </c>
       <c r="K44" s="2">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="L44" s="2">
         <v>1</v>
@@ -3632,10 +3628,10 @@
         <v>0</v>
       </c>
       <c r="N44" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O44" s="2">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="P44" s="2">
         <v>9</v>
@@ -3653,7 +3649,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45">
       <c r="A45" s="2" t="s">
         <v>36</v>
       </c>
@@ -3670,19 +3666,19 @@
         <v>145</v>
       </c>
       <c r="F45" s="2">
-        <v>1924</v>
+        <v>1939</v>
       </c>
       <c r="G45" s="2">
-        <v>2407</v>
+        <v>2456</v>
       </c>
       <c r="H45" s="2">
-        <v>2387</v>
+        <v>2435</v>
       </c>
       <c r="I45" s="2">
-        <v>1014</v>
+        <v>1037</v>
       </c>
       <c r="J45" s="2">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="K45" s="2">
         <v>10</v>
@@ -3700,7 +3696,7 @@
         <v>5</v>
       </c>
       <c r="P45" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q45" s="2" t="s">
         <v>171</v>
@@ -3715,7 +3711,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46">
       <c r="A46" s="2" t="s">
         <v>37</v>
       </c>
@@ -3732,22 +3728,22 @@
         <v>146</v>
       </c>
       <c r="F46" s="2">
-        <v>21760</v>
+        <v>22588</v>
       </c>
       <c r="G46" s="2">
-        <v>32832</v>
+        <v>34447</v>
       </c>
       <c r="H46" s="2">
-        <v>32586</v>
+        <v>34186</v>
       </c>
       <c r="I46" s="2">
-        <v>18738</v>
+        <v>19609</v>
       </c>
       <c r="J46" s="2">
-        <v>6331</v>
+        <v>6618</v>
       </c>
       <c r="K46" s="2">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="L46" s="2">
         <v>0</v>
@@ -3759,7 +3755,7 @@
         <v>6</v>
       </c>
       <c r="O46" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P46" s="2">
         <v>10</v>
@@ -3777,12 +3773,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47">
       <c r="A47" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>74</v>
@@ -3839,7 +3835,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="48" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48">
       <c r="A48" s="2" t="s">
         <v>38</v>
       </c>
@@ -3856,19 +3852,19 @@
         <v>147</v>
       </c>
       <c r="F48" s="2">
-        <v>12655</v>
+        <v>12658</v>
       </c>
       <c r="G48" s="2">
-        <v>14187</v>
+        <v>14190</v>
       </c>
       <c r="H48" s="2">
-        <v>14084</v>
+        <v>14087</v>
       </c>
       <c r="I48" s="2">
-        <v>9964</v>
+        <v>9967</v>
       </c>
       <c r="J48" s="2">
-        <v>3325</v>
+        <v>3326</v>
       </c>
       <c r="K48" s="2">
         <v>18</v>
@@ -3901,12 +3897,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49">
       <c r="A49" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>74</v>
@@ -3963,7 +3959,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50">
       <c r="A50" s="2" t="s">
         <v>40</v>
       </c>
@@ -3971,7 +3967,7 @@
         <v>70</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>93</v>
@@ -3980,19 +3976,19 @@
         <v>148</v>
       </c>
       <c r="F50" s="2">
-        <v>6803</v>
+        <v>6809</v>
       </c>
       <c r="G50" s="2">
-        <v>7324</v>
+        <v>7331</v>
       </c>
       <c r="H50" s="2">
-        <v>7279</v>
+        <v>7286</v>
       </c>
       <c r="I50" s="2">
-        <v>4493</v>
+        <v>4499</v>
       </c>
       <c r="J50" s="2">
-        <v>1962</v>
+        <v>1966</v>
       </c>
       <c r="K50" s="2">
         <v>10</v>
@@ -4025,7 +4021,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51">
       <c r="A51" s="2" t="s">
         <v>39</v>
       </c>
@@ -4033,7 +4029,7 @@
         <v>70</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>93</v>
@@ -4042,22 +4038,22 @@
         <v>149</v>
       </c>
       <c r="F51" s="2">
-        <v>58243</v>
+        <v>60389</v>
       </c>
       <c r="G51" s="2">
-        <v>84930</v>
+        <v>89887</v>
       </c>
       <c r="H51" s="2">
-        <v>84332</v>
+        <v>89237</v>
       </c>
       <c r="I51" s="2">
-        <v>47945</v>
+        <v>50501</v>
       </c>
       <c r="J51" s="2">
-        <v>22915</v>
+        <v>24060</v>
       </c>
       <c r="K51" s="2">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="L51" s="2">
         <v>0</v>
@@ -4066,13 +4062,13 @@
         <v>2</v>
       </c>
       <c r="N51" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O51" s="2">
-        <v>426</v>
+        <v>452</v>
       </c>
       <c r="P51" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q51" s="2" t="s">
         <v>171</v>
@@ -4087,7 +4083,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="52" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52">
       <c r="A52" s="2" t="s">
         <v>41</v>
       </c>
@@ -4095,46 +4091,46 @@
         <v>70</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>108</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="F52" s="2">
-        <v>11500</v>
+        <v>11690</v>
       </c>
       <c r="G52" s="2">
-        <v>17075</v>
+        <v>17371</v>
       </c>
       <c r="H52" s="2">
-        <v>16470</v>
+        <v>16758</v>
       </c>
       <c r="I52" s="2">
-        <v>6477</v>
+        <v>6584</v>
       </c>
       <c r="J52" s="2">
-        <v>2714</v>
+        <v>2762</v>
       </c>
       <c r="K52" s="2">
-        <v>779</v>
+        <v>792</v>
       </c>
       <c r="L52" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M52" s="2">
         <v>27</v>
       </c>
       <c r="N52" s="2">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="O52" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P52" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="Q52" s="2" t="s">
         <v>171</v>
@@ -4149,7 +4145,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="53" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53">
       <c r="A53" s="2" t="s">
         <v>41</v>
       </c>
@@ -4163,25 +4159,25 @@
         <v>96</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F53" s="2">
-        <v>24101</v>
+        <v>25384</v>
       </c>
       <c r="G53" s="2">
-        <v>31180</v>
+        <v>33181</v>
       </c>
       <c r="H53" s="2">
-        <v>30912</v>
+        <v>32896</v>
       </c>
       <c r="I53" s="2">
-        <v>21198</v>
+        <v>22489</v>
       </c>
       <c r="J53" s="2">
-        <v>9777</v>
+        <v>10313</v>
       </c>
       <c r="K53" s="2">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L53" s="2">
         <v>2</v>
@@ -4190,10 +4186,10 @@
         <v>0</v>
       </c>
       <c r="N53" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O53" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P53" s="2">
         <v>8</v>
@@ -4211,7 +4207,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="54" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54">
       <c r="A54" s="2" t="s">
         <v>42</v>
       </c>
@@ -4225,40 +4221,40 @@
         <v>96</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F54" s="2">
-        <v>132333</v>
+        <v>137323</v>
       </c>
       <c r="G54" s="2">
-        <v>192063</v>
+        <v>202507</v>
       </c>
       <c r="H54" s="2">
-        <v>191150</v>
+        <v>201543</v>
       </c>
       <c r="I54" s="2">
-        <v>119667</v>
+        <v>125501</v>
       </c>
       <c r="J54" s="2">
-        <v>58870</v>
+        <v>61456</v>
       </c>
       <c r="K54" s="2">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="L54" s="2">
         <v>1</v>
       </c>
       <c r="M54" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N54" s="2">
         <v>55</v>
       </c>
       <c r="O54" s="2">
-        <v>348</v>
+        <v>372</v>
       </c>
       <c r="P54" s="2">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Q54" s="2" t="s">
         <v>171</v>
@@ -4273,12 +4269,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55">
       <c r="A55" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>74</v>
@@ -4287,7 +4283,7 @@
         <v>81</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F55" s="2">
         <v>781</v>
@@ -4335,12 +4331,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56">
       <c r="A56" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>74</v>
@@ -4349,7 +4345,7 @@
         <v>81</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F56" s="2">
         <v>1955</v>
@@ -4397,7 +4393,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57">
       <c r="A57" s="2" t="s">
         <v>44</v>
       </c>
@@ -4405,31 +4401,31 @@
         <v>70</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>82</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F57" s="2">
-        <v>187004</v>
+        <v>187895</v>
       </c>
       <c r="G57" s="2">
-        <v>258163</v>
+        <v>259585</v>
       </c>
       <c r="H57" s="2">
-        <v>256819</v>
+        <v>258236</v>
       </c>
       <c r="I57" s="2">
-        <v>199778</v>
+        <v>200859</v>
       </c>
       <c r="J57" s="2">
-        <v>67903</v>
+        <v>68283</v>
       </c>
       <c r="K57" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="L57" s="2">
         <v>1</v>
@@ -4438,10 +4434,10 @@
         <v>5</v>
       </c>
       <c r="N57" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O57" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P57" s="2">
         <v>47</v>
@@ -4459,7 +4455,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="58" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58">
       <c r="A58" s="2" t="s">
         <v>43</v>
       </c>
@@ -4467,13 +4463,13 @@
         <v>70</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>82</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F58" s="2">
         <v>395</v>
@@ -4521,7 +4517,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59">
       <c r="A59" s="2" t="s">
         <v>45</v>
       </c>
@@ -4535,7 +4531,7 @@
         <v>102</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F59" s="2">
         <v>0</v>
@@ -4583,7 +4579,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="60" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60">
       <c r="A60" s="2" t="s">
         <v>46</v>
       </c>
@@ -4591,13 +4587,13 @@
         <v>71</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F60" s="2">
         <v>0</v>
@@ -4645,7 +4641,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="61" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61">
       <c r="A61" s="2" t="s">
         <v>47</v>
       </c>
@@ -4653,13 +4649,13 @@
         <v>71</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>99</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F61" s="2">
         <v>0</v>
@@ -4707,7 +4703,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="62" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62">
       <c r="A62" s="2" t="s">
         <v>47</v>
       </c>
@@ -4715,13 +4711,13 @@
         <v>71</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>83</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F62" s="2">
         <v>0</v>
@@ -4769,7 +4765,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63">
       <c r="A63" s="2" t="s">
         <v>48</v>
       </c>
@@ -4777,13 +4773,13 @@
         <v>71</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>100</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F63" s="2">
         <v>0</v>
@@ -4831,7 +4827,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="64" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64">
       <c r="A64" s="2" t="s">
         <v>48</v>
       </c>
@@ -4845,7 +4841,7 @@
         <v>84</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F64" s="2">
         <v>0</v>
@@ -4893,7 +4889,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="65" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65">
       <c r="A65" s="2" t="s">
         <v>49</v>
       </c>
@@ -4901,13 +4897,13 @@
         <v>71</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>101</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F65" s="2">
         <v>0</v>
@@ -4955,7 +4951,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="66" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66">
       <c r="A66" s="2" t="s">
         <v>50</v>
       </c>
@@ -4963,13 +4959,13 @@
         <v>71</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>101</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F66" s="2">
         <v>0</v>
@@ -5017,7 +5013,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="67" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67">
       <c r="A67" s="2" t="s">
         <v>49</v>
       </c>
@@ -5031,7 +5027,7 @@
         <v>85</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F67" s="2">
         <v>0</v>
@@ -5079,7 +5075,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="68" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68">
       <c r="A68" s="2" t="s">
         <v>50</v>
       </c>
@@ -5093,7 +5089,7 @@
         <v>85</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F68" s="2">
         <v>0</v>
@@ -5141,7 +5137,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="69" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69">
       <c r="A69" s="2" t="s">
         <v>51</v>
       </c>
@@ -5149,13 +5145,13 @@
         <v>71</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>103</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F69" s="2">
         <v>0</v>
@@ -5203,7 +5199,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="70" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70">
       <c r="A70" s="2" t="s">
         <v>52</v>
       </c>
@@ -5211,13 +5207,13 @@
         <v>71</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>103</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F70" s="2">
         <v>0</v>
@@ -5265,7 +5261,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="71" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71">
       <c r="A71" s="2" t="s">
         <v>51</v>
       </c>
@@ -5273,13 +5269,13 @@
         <v>71</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>87</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F71" s="2">
         <v>0</v>
@@ -5327,7 +5323,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="72" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72">
       <c r="A72" s="2" t="s">
         <v>53</v>
       </c>
@@ -5335,13 +5331,13 @@
         <v>71</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>87</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F72" s="2">
         <v>0</v>
@@ -5389,7 +5385,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="73" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="73">
       <c r="A73" s="2" t="s">
         <v>54</v>
       </c>
@@ -5403,7 +5399,7 @@
         <v>104</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F73" s="2">
         <v>0</v>
@@ -5451,7 +5447,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="74" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74">
       <c r="A74" s="2" t="s">
         <v>55</v>
       </c>
@@ -5459,13 +5455,13 @@
         <v>71</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>105</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F74" s="2">
         <v>0</v>
@@ -5513,7 +5509,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="75" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75">
       <c r="A75" s="2" t="s">
         <v>56</v>
       </c>
@@ -5521,13 +5517,13 @@
         <v>71</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>88</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F75" s="2">
         <v>0</v>
@@ -5575,7 +5571,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="76" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76">
       <c r="A76" s="2" t="s">
         <v>57</v>
       </c>
@@ -5583,13 +5579,13 @@
         <v>71</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>88</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F76" s="2">
         <v>0</v>
@@ -5637,7 +5633,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="77" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77">
       <c r="A77" s="2" t="s">
         <v>57</v>
       </c>
@@ -5651,7 +5647,7 @@
         <v>89</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F77" s="2">
         <v>0</v>
@@ -5699,7 +5695,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="78" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="78">
       <c r="A78" s="2" t="s">
         <v>56</v>
       </c>
@@ -5713,7 +5709,7 @@
         <v>89</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F78" s="2">
         <v>0</v>
@@ -5761,7 +5757,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="79" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="79">
       <c r="A79" s="2" t="s">
         <v>58</v>
       </c>
@@ -5769,13 +5765,13 @@
         <v>71</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>106</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F79" s="2">
         <v>0</v>
@@ -5823,7 +5819,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="80" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="80">
       <c r="A80" s="2" t="s">
         <v>58</v>
       </c>
@@ -5831,13 +5827,13 @@
         <v>71</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>90</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F80" s="2">
         <v>0</v>
@@ -5885,7 +5881,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="81" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="81">
       <c r="A81" s="2" t="s">
         <v>59</v>
       </c>
@@ -5899,7 +5895,7 @@
         <v>91</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F81" s="2">
         <v>0</v>
@@ -5947,7 +5943,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82">
       <c r="A82" s="2" t="s">
         <v>60</v>
       </c>
@@ -5961,7 +5957,7 @@
         <v>91</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F82" s="2">
         <v>0</v>
@@ -6009,12 +6005,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="83">
       <c r="A83" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>79</v>
@@ -6023,7 +6019,7 @@
         <v>92</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F83" s="2">
         <v>0</v>
@@ -6071,12 +6067,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="84">
       <c r="A84" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>79</v>
@@ -6085,7 +6081,7 @@
         <v>92</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F84" s="2">
         <v>0</v>
@@ -6133,7 +6129,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="85">
       <c r="A85" s="2" t="s">
         <v>61</v>
       </c>
@@ -6141,13 +6137,13 @@
         <v>71</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>107</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F85" s="2">
         <v>0</v>
@@ -6195,7 +6191,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="86">
       <c r="A86" s="2" t="s">
         <v>62</v>
       </c>
@@ -6203,13 +6199,13 @@
         <v>71</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>107</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F86" s="2">
         <v>0</v>
@@ -6257,7 +6253,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="87">
       <c r="A87" s="2" t="s">
         <v>62</v>
       </c>
@@ -6271,7 +6267,7 @@
         <v>93</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F87" s="2">
         <v>0</v>
@@ -6319,7 +6315,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="88">
       <c r="A88" s="2" t="s">
         <v>61</v>
       </c>
@@ -6333,7 +6329,7 @@
         <v>93</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F88" s="2">
         <v>0</v>
@@ -6381,7 +6377,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="89" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="89">
       <c r="A89" s="2" t="s">
         <v>63</v>
       </c>
@@ -6389,13 +6385,13 @@
         <v>71</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>94</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F89" s="2">
         <v>0</v>
@@ -6443,7 +6439,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="90" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="90">
       <c r="A90" s="2" t="s">
         <v>64</v>
       </c>
@@ -6451,13 +6447,13 @@
         <v>71</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>94</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F90" s="2">
         <v>0</v>
@@ -6505,7 +6501,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="91" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="91">
       <c r="A91" s="2" t="s">
         <v>64</v>
       </c>
@@ -6513,13 +6509,13 @@
         <v>71</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>95</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F91" s="2">
         <v>0</v>
@@ -6567,7 +6563,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="92" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="92">
       <c r="A92" s="2" t="s">
         <v>63</v>
       </c>
@@ -6575,13 +6571,13 @@
         <v>71</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>95</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F92" s="2">
         <v>0</v>
@@ -6629,7 +6625,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="93" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="93">
       <c r="A93" s="2" t="s">
         <v>65</v>
       </c>
@@ -6637,13 +6633,13 @@
         <v>71</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>81</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F93" s="2">
         <v>1498</v>
@@ -6691,7 +6687,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="94" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="94">
       <c r="A94" s="2" t="s">
         <v>66</v>
       </c>
@@ -6705,7 +6701,7 @@
         <v>108</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F94" s="2">
         <v>0</v>
@@ -6753,7 +6749,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="95" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="95">
       <c r="A95" s="2" t="s">
         <v>67</v>
       </c>
@@ -6767,7 +6763,7 @@
         <v>108</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F95" s="2">
         <v>0</v>
@@ -6815,7 +6811,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="96" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="96">
       <c r="A96" s="2" t="s">
         <v>67</v>
       </c>
@@ -6823,13 +6819,13 @@
         <v>71</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>96</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F96" s="2">
         <v>0</v>
@@ -6877,7 +6873,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="97" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="97">
       <c r="A97" s="2" t="s">
         <v>66</v>
       </c>
@@ -6885,13 +6881,13 @@
         <v>71</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>96</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F97" s="2">
         <v>0</v>
@@ -6939,7 +6935,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="98" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="98">
       <c r="A98" s="2" t="s">
         <v>65</v>
       </c>
@@ -6953,7 +6949,7 @@
         <v>82</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F98" s="2">
         <v>0</v>
@@ -7001,8 +6997,69 @@
         <v>176</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F99" s="2">
+        <v>757680</v>
+      </c>
+      <c r="G99" s="2">
+        <v>2114220</v>
+      </c>
+      <c r="H99" s="2">
+        <v>2097452</v>
+      </c>
+      <c r="I99" s="2">
+        <v>1295906</v>
+      </c>
+      <c r="J99" s="2">
+        <v>533136</v>
+      </c>
+      <c r="K99" s="2">
+        <v>8180</v>
+      </c>
+      <c r="L99" s="2">
+        <v>218</v>
+      </c>
+      <c r="M99" s="2">
+        <v>149</v>
+      </c>
+      <c r="N99" s="2">
+        <v>4268</v>
+      </c>
+      <c r="O99" s="2">
+        <v>4786</v>
+      </c>
+      <c r="P99" s="2">
+        <v>1060</v>
+      </c>
+      <c r="Q99" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R99" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S99" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T99" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/June.xlsx
+++ b/data/June.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9390FBC1-9C05-4EC6-81D3-767716591BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,34 +15,31 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Author</author>
+    <author>ผู้สร้าง</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
+            <sz val="12"/>
             <rFont val="Arial"/>
-            <color/>
-            <sz val="12"/>
           </rPr>
-          <t xml:space="preserve">This is a reach-based metric. Reach-based metrics are de-duplicated metrics so you might see different numbers based on the level at which you are viewing data.</t>
+          <t>This is a reach-based metric. Reach-based metrics are de-duplicated metrics so you might see different numbers based on the level at which you are viewing data.</t>
         </r>
         <r>
           <rPr>
+            <sz val="12"/>
             <rFont val="Arial"/>
-            <color/>
-            <sz val="12"/>
           </rPr>
           <t xml:space="preserve">     </t>
         </r>
         <r>
           <rPr>
+            <sz val="12"/>
             <rFont val="Arial"/>
-            <color/>
-            <sz val="12"/>
           </rPr>
           <t xml:space="preserve">     </t>
         </r>
@@ -52,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="175">
   <si>
     <t>Ad name</t>
   </si>
@@ -258,9 +256,6 @@
     <t>หมดกองนี้ ลูกค้ารับไปเลย 23,XXX บาท</t>
   </si>
   <si>
-    <t>Total of 97 results</t>
-  </si>
-  <si>
     <t>Primary status</t>
   </si>
   <si>
@@ -526,9 +521,6 @@
   </si>
   <si>
     <t>2532.61</t>
-  </si>
-  <si>
-    <t>81737.65</t>
   </si>
   <si>
     <t>Reach</t>
@@ -588,8 +580,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -597,17 +589,19 @@
       <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="12"/>
-      <color/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
-      <color/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -645,136 +639,140 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<theme xmlns="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
-  <themeElements>
-    <clrScheme name="Office">
-      <dk1>
-        <sysClr val="windowText" lastClr="000000"/>
-      </dk1>
-      <lt1>
-        <sysClr val="window" lastClr="FFFFFF"/>
-      </lt1>
-      <dk2>
-        <srgbClr val="44546A"/>
-      </dk2>
-      <lt2>
-        <srgbClr val="E7E6E6"/>
-      </lt2>
-      <accent1>
-        <srgbClr val="5B9BD5"/>
-      </accent1>
-      <accent2>
-        <srgbClr val="ED7D31"/>
-      </accent2>
-      <accent3>
-        <srgbClr val="A5A5A5"/>
-      </accent3>
-      <accent4>
-        <srgbClr val="FFC000"/>
-      </accent4>
-      <accent5>
-        <srgbClr val="4472C4"/>
-      </accent5>
-      <accent6>
-        <srgbClr val="70AD47"/>
-      </accent6>
-      <hlink>
-        <srgbClr val="0563C1"/>
-      </hlink>
-      <folHlink>
-        <srgbClr val="954F72"/>
-      </folHlink>
-    </clrScheme>
-    <fontScheme name="Office">
-      <majorFont>
-        <latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <ea typeface=""/>
-        <cs typeface=""/>
-        <font script="Jpan" typeface="游ゴシック Light"/>
-        <font script="Hang" typeface="맑은 고딕"/>
-        <font script="Hans" typeface="等线 Light"/>
-        <font script="Hant" typeface="新細明體"/>
-        <font script="Arab" typeface="Times New Roman"/>
-        <font script="Hebr" typeface="Times New Roman"/>
-        <font script="Thai" typeface="Tahoma"/>
-        <font script="Ethi" typeface="Nyala"/>
-        <font script="Beng" typeface="Vrinda"/>
-        <font script="Gujr" typeface="Shruti"/>
-        <font script="Khmr" typeface="MoolBoran"/>
-        <font script="Knda" typeface="Tunga"/>
-        <font script="Guru" typeface="Raavi"/>
-        <font script="Cans" typeface="Euphemia"/>
-        <font script="Cher" typeface="Plantagenet Cherokee"/>
-        <font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <font script="Tibt" typeface="Microsoft Himalaya"/>
-        <font script="Thaa" typeface="MV Boli"/>
-        <font script="Deva" typeface="Mangal"/>
-        <font script="Telu" typeface="Gautami"/>
-        <font script="Taml" typeface="Latha"/>
-        <font script="Syrc" typeface="Estrangelo Edessa"/>
-        <font script="Orya" typeface="Kalinga"/>
-        <font script="Mlym" typeface="Kartika"/>
-        <font script="Laoo" typeface="DokChampa"/>
-        <font script="Sinh" typeface="Iskoola Pota"/>
-        <font script="Mong" typeface="Mongolian Baiti"/>
-        <font script="Viet" typeface="Times New Roman"/>
-        <font script="Uigh" typeface="Microsoft Uighur"/>
-        <font script="Geor" typeface="Sylfaen"/>
-      </majorFont>
-      <minorFont>
-        <latin typeface="Calibri" panose="020F0502020204030204"/>
-        <ea typeface=""/>
-        <cs typeface=""/>
-        <font script="Jpan" typeface="游ゴシック"/>
-        <font script="Hang" typeface="맑은 고딕"/>
-        <font script="Hans" typeface="等线"/>
-        <font script="Hant" typeface="新細明體"/>
-        <font script="Arab" typeface="Arial"/>
-        <font script="Hebr" typeface="Arial"/>
-        <font script="Thai" typeface="Tahoma"/>
-        <font script="Ethi" typeface="Nyala"/>
-        <font script="Beng" typeface="Vrinda"/>
-        <font script="Gujr" typeface="Shruti"/>
-        <font script="Khmr" typeface="DaunPenh"/>
-        <font script="Knda" typeface="Tunga"/>
-        <font script="Guru" typeface="Raavi"/>
-        <font script="Cans" typeface="Euphemia"/>
-        <font script="Cher" typeface="Plantagenet Cherokee"/>
-        <font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <font script="Tibt" typeface="Microsoft Himalaya"/>
-        <font script="Thaa" typeface="MV Boli"/>
-        <font script="Deva" typeface="Mangal"/>
-        <font script="Telu" typeface="Gautami"/>
-        <font script="Taml" typeface="Latha"/>
-        <font script="Syrc" typeface="Estrangelo Edessa"/>
-        <font script="Orya" typeface="Kalinga"/>
-        <font script="Mlym" typeface="Kartika"/>
-        <font script="Laoo" typeface="DokChampa"/>
-        <font script="Sinh" typeface="Iskoola Pota"/>
-        <font script="Mong" typeface="Mongolian Baiti"/>
-        <font script="Viet" typeface="Arial"/>
-        <font script="Uigh" typeface="Microsoft Uighur"/>
-        <font script="Geor" typeface="Sylfaen"/>
-      </minorFont>
-    </fontScheme>
-    <fmtScheme name="Office">
-      <fillStyleLst>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -830,8 +828,8 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-      </fillStyleLst>
-      <lnStyleLst>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -853,8 +851,8 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-      </lnStyleLst>
-      <effectStyleLst>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst/>
         </a:effectStyle>
@@ -870,8 +868,8 @@
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
-      </effectStyleLst>
-      <bgFillStyleLst>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -908,96 +906,96 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-      </bgFillStyleLst>
-    </fmtScheme>
-  </themeElements>
-  <objectDefaults/>
-  <extraClrSchemeLst/>
-</theme>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T98"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="T1" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F2" s="2">
         <v>495</v>
@@ -1033,33 +1031,33 @@
         <v>3</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F3" s="2">
         <v>529</v>
@@ -1095,33 +1093,33 @@
         <v>6</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F4" s="2">
         <v>160854</v>
@@ -1157,33 +1155,33 @@
         <v>34</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F5" s="2">
         <v>1683</v>
@@ -1219,33 +1217,33 @@
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F6" s="2">
         <v>41778</v>
@@ -1281,33 +1279,33 @@
         <v>9</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F7" s="2">
         <v>8097</v>
@@ -1343,33 +1341,33 @@
         <v>2</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F8" s="2">
         <v>19886</v>
@@ -1405,33 +1403,33 @@
         <v>4</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F9" s="2">
         <v>782</v>
@@ -1467,33 +1465,33 @@
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F10" s="2">
         <v>58078</v>
@@ -1529,33 +1527,33 @@
         <v>16</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F11" s="2">
         <v>353</v>
@@ -1591,33 +1589,33 @@
         <v>0</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F12" s="2">
         <v>5642</v>
@@ -1653,33 +1651,33 @@
         <v>0</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F13" s="2">
         <v>2788</v>
@@ -1715,33 +1713,33 @@
         <v>22</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F14" s="2">
         <v>48515</v>
@@ -1777,33 +1775,33 @@
         <v>16</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F15" s="2">
         <v>65866</v>
@@ -1839,33 +1837,33 @@
         <v>29</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F16" s="2">
         <v>1322</v>
@@ -1901,33 +1899,33 @@
         <v>19</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F17" s="2">
         <v>41343</v>
@@ -1963,33 +1961,33 @@
         <v>9</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F18" s="2">
         <v>13674</v>
@@ -2025,33 +2023,33 @@
         <v>3</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F19" s="2">
         <v>12677</v>
@@ -2087,33 +2085,33 @@
         <v>4</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F20" s="2">
         <v>60</v>
@@ -2149,33 +2147,33 @@
         <v>0</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F21" s="2">
         <v>1309</v>
@@ -2211,33 +2209,33 @@
         <v>17</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F22" s="2">
         <v>30399</v>
@@ -2273,33 +2271,33 @@
         <v>9</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F23" s="2">
         <v>44346</v>
@@ -2335,33 +2333,33 @@
         <v>5</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F24" s="2">
         <v>24977</v>
@@ -2397,33 +2395,33 @@
         <v>3</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F25" s="2">
         <v>4436</v>
@@ -2459,33 +2457,33 @@
         <v>85</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F26" s="2">
         <v>1108</v>
@@ -2521,33 +2519,33 @@
         <v>0</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F27" s="2">
         <v>802</v>
@@ -2583,33 +2581,33 @@
         <v>30</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F28" s="2">
         <v>76578</v>
@@ -2645,33 +2643,33 @@
         <v>24</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F29" s="2">
         <v>1607</v>
@@ -2707,33 +2705,33 @@
         <v>24</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F30" s="2">
         <v>7842</v>
@@ -2769,33 +2767,33 @@
         <v>6</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F31" s="2">
         <v>13459</v>
@@ -2831,33 +2829,33 @@
         <v>2</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F32" s="2">
         <v>1474</v>
@@ -2893,33 +2891,33 @@
         <v>20</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F33" s="2">
         <v>35613</v>
@@ -2955,33 +2953,33 @@
         <v>8</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F34" s="2">
         <v>5864</v>
@@ -3017,33 +3015,33 @@
         <v>0</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F35" s="2">
         <v>1540</v>
@@ -3079,33 +3077,33 @@
         <v>11</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F36" s="2">
         <v>23937</v>
@@ -3141,33 +3139,33 @@
         <v>3</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F37" s="2">
         <v>10663</v>
@@ -3203,33 +3201,33 @@
         <v>92</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F38" s="2">
         <v>91034</v>
@@ -3265,33 +3263,33 @@
         <v>23</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F39" s="2">
         <v>480</v>
@@ -3327,33 +3325,33 @@
         <v>0</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F40" s="2">
         <v>2010</v>
@@ -3389,33 +3387,33 @@
         <v>24</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F41" s="2">
         <v>7991</v>
@@ -3451,33 +3449,33 @@
         <v>2</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F42" s="2">
         <v>15380</v>
@@ -3513,33 +3511,33 @@
         <v>116</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F43" s="2">
         <v>67764</v>
@@ -3575,33 +3573,33 @@
         <v>24</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F44" s="2">
         <v>17704</v>
@@ -3637,33 +3635,33 @@
         <v>9</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F45" s="2">
         <v>1939</v>
@@ -3699,33 +3697,33 @@
         <v>2</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T45" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F46" s="2">
         <v>22588</v>
@@ -3761,33 +3759,33 @@
         <v>10</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="47">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F47" s="2">
         <v>1321</v>
@@ -3823,33 +3821,33 @@
         <v>18</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R47" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T47" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F48" s="2">
         <v>12658</v>
@@ -3885,33 +3883,33 @@
         <v>2</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T48" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F49" s="2">
         <v>1362</v>
@@ -3947,33 +3945,33 @@
         <v>16</v>
       </c>
       <c r="Q49" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R49" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F50" s="2">
         <v>6809</v>
@@ -4009,33 +4007,33 @@
         <v>0</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R50" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S50" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F51" s="2">
         <v>60389</v>
@@ -4071,33 +4069,33 @@
         <v>8</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T51" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F52" s="2">
         <v>11690</v>
@@ -4133,33 +4131,33 @@
         <v>95</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R52" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T52" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F53" s="2">
         <v>25384</v>
@@ -4195,33 +4193,33 @@
         <v>8</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S53" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T53" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F54" s="2">
         <v>137323</v>
@@ -4257,33 +4255,33 @@
         <v>57</v>
       </c>
       <c r="Q54" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R54" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S54" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T54" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="55">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F55" s="2">
         <v>781</v>
@@ -4319,33 +4317,33 @@
         <v>4</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R55" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S55" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T55" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F56" s="2">
         <v>1955</v>
@@ -4381,33 +4379,33 @@
         <v>29</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R56" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T56" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="57">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F57" s="2">
         <v>187895</v>
@@ -4443,33 +4441,33 @@
         <v>47</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R57" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T57" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="58">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F58" s="2">
         <v>395</v>
@@ -4505,33 +4503,33 @@
         <v>0</v>
       </c>
       <c r="Q58" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R58" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T58" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="59">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F59" s="2">
         <v>0</v>
@@ -4567,33 +4565,33 @@
         <v>0</v>
       </c>
       <c r="Q59" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R59" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T59" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="60">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F60" s="2">
         <v>0</v>
@@ -4629,33 +4627,33 @@
         <v>0</v>
       </c>
       <c r="Q60" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T60" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="61">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F61" s="2">
         <v>0</v>
@@ -4691,33 +4689,33 @@
         <v>0</v>
       </c>
       <c r="Q61" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R61" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F62" s="2">
         <v>0</v>
@@ -4753,33 +4751,33 @@
         <v>0</v>
       </c>
       <c r="Q62" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R62" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T62" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="63">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F63" s="2">
         <v>0</v>
@@ -4815,33 +4813,33 @@
         <v>0</v>
       </c>
       <c r="Q63" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R63" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T63" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="64">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F64" s="2">
         <v>0</v>
@@ -4877,33 +4875,33 @@
         <v>0</v>
       </c>
       <c r="Q64" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R64" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T64" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="65">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F65" s="2">
         <v>0</v>
@@ -4939,33 +4937,33 @@
         <v>0</v>
       </c>
       <c r="Q65" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R65" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T65" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="66">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F66" s="2">
         <v>0</v>
@@ -5001,33 +4999,33 @@
         <v>0</v>
       </c>
       <c r="Q66" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R66" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T66" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="67">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F67" s="2">
         <v>0</v>
@@ -5063,33 +5061,33 @@
         <v>0</v>
       </c>
       <c r="Q67" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R67" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S67" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T67" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="68">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F68" s="2">
         <v>0</v>
@@ -5125,33 +5123,33 @@
         <v>0</v>
       </c>
       <c r="Q68" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R68" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="69">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F69" s="2">
         <v>0</v>
@@ -5187,33 +5185,33 @@
         <v>0</v>
       </c>
       <c r="Q69" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R69" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S69" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T69" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="70">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F70" s="2">
         <v>0</v>
@@ -5249,33 +5247,33 @@
         <v>0</v>
       </c>
       <c r="Q70" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R70" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S70" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T70" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="71">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F71" s="2">
         <v>0</v>
@@ -5311,33 +5309,33 @@
         <v>0</v>
       </c>
       <c r="Q71" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R71" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S71" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T71" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="72">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F72" s="2">
         <v>0</v>
@@ -5373,33 +5371,33 @@
         <v>0</v>
       </c>
       <c r="Q72" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R72" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S72" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T72" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="73">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F73" s="2">
         <v>0</v>
@@ -5435,33 +5433,33 @@
         <v>0</v>
       </c>
       <c r="Q73" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R73" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S73" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T73" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="74">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F74" s="2">
         <v>0</v>
@@ -5497,33 +5495,33 @@
         <v>0</v>
       </c>
       <c r="Q74" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R74" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S74" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T74" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="75">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F75" s="2">
         <v>0</v>
@@ -5559,33 +5557,33 @@
         <v>0</v>
       </c>
       <c r="Q75" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R75" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S75" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T75" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="76">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F76" s="2">
         <v>0</v>
@@ -5621,33 +5619,33 @@
         <v>0</v>
       </c>
       <c r="Q76" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R76" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S76" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T76" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="77">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F77" s="2">
         <v>0</v>
@@ -5683,33 +5681,33 @@
         <v>0</v>
       </c>
       <c r="Q77" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R77" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S77" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T77" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="78">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F78" s="2">
         <v>0</v>
@@ -5745,33 +5743,33 @@
         <v>0</v>
       </c>
       <c r="Q78" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R78" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S78" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T78" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="79">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F79" s="2">
         <v>0</v>
@@ -5807,33 +5805,33 @@
         <v>0</v>
       </c>
       <c r="Q79" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R79" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S79" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T79" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="80">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F80" s="2">
         <v>0</v>
@@ -5869,33 +5867,33 @@
         <v>0</v>
       </c>
       <c r="Q80" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R80" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S80" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T80" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="81">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F81" s="2">
         <v>0</v>
@@ -5931,33 +5929,33 @@
         <v>0</v>
       </c>
       <c r="Q81" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R81" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S81" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T81" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="82">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F82" s="2">
         <v>0</v>
@@ -5993,33 +5991,33 @@
         <v>0</v>
       </c>
       <c r="Q82" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R82" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S82" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T82" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="83">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F83" s="2">
         <v>0</v>
@@ -6055,33 +6053,33 @@
         <v>0</v>
       </c>
       <c r="Q83" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R83" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S83" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T83" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="84">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F84" s="2">
         <v>0</v>
@@ -6117,33 +6115,33 @@
         <v>0</v>
       </c>
       <c r="Q84" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R84" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S84" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T84" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="85">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F85" s="2">
         <v>0</v>
@@ -6179,33 +6177,33 @@
         <v>0</v>
       </c>
       <c r="Q85" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R85" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S85" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T85" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="86">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F86" s="2">
         <v>0</v>
@@ -6241,33 +6239,33 @@
         <v>0</v>
       </c>
       <c r="Q86" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R86" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S86" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T86" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="87">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F87" s="2">
         <v>0</v>
@@ -6303,33 +6301,33 @@
         <v>0</v>
       </c>
       <c r="Q87" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R87" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S87" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T87" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="88">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F88" s="2">
         <v>0</v>
@@ -6365,33 +6363,33 @@
         <v>0</v>
       </c>
       <c r="Q88" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R88" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S88" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T88" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="89">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F89" s="2">
         <v>0</v>
@@ -6427,33 +6425,33 @@
         <v>0</v>
       </c>
       <c r="Q89" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R89" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S89" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T89" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="90">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F90" s="2">
         <v>0</v>
@@ -6489,33 +6487,33 @@
         <v>0</v>
       </c>
       <c r="Q90" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R90" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S90" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T90" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="91">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F91" s="2">
         <v>0</v>
@@ -6551,33 +6549,33 @@
         <v>0</v>
       </c>
       <c r="Q91" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R91" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S91" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T91" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="92">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F92" s="2">
         <v>0</v>
@@ -6613,33 +6611,33 @@
         <v>0</v>
       </c>
       <c r="Q92" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R92" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S92" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T92" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="93">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>65</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F93" s="2">
         <v>1498</v>
@@ -6675,33 +6673,33 @@
         <v>50</v>
       </c>
       <c r="Q93" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R93" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S93" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T93" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="94">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F94" s="2">
         <v>0</v>
@@ -6737,33 +6735,33 @@
         <v>0</v>
       </c>
       <c r="Q94" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R94" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S94" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T94" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="95">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F95" s="2">
         <v>0</v>
@@ -6799,33 +6797,33 @@
         <v>0</v>
       </c>
       <c r="Q95" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R95" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S95" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T95" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="96">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F96" s="2">
         <v>0</v>
@@ -6861,33 +6859,33 @@
         <v>0</v>
       </c>
       <c r="Q96" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R96" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S96" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T96" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="97">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F97" s="2">
         <v>0</v>
@@ -6923,33 +6921,33 @@
         <v>0</v>
       </c>
       <c r="Q97" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R97" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S97" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T97" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="98">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>65</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F98" s="2">
         <v>0</v>
@@ -6985,81 +6983,20 @@
         <v>0</v>
       </c>
       <c r="Q98" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R98" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S98" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T98" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F99" s="2">
-        <v>757680</v>
-      </c>
-      <c r="G99" s="2">
-        <v>2114220</v>
-      </c>
-      <c r="H99" s="2">
-        <v>2097452</v>
-      </c>
-      <c r="I99" s="2">
-        <v>1295906</v>
-      </c>
-      <c r="J99" s="2">
-        <v>533136</v>
-      </c>
-      <c r="K99" s="2">
-        <v>8180</v>
-      </c>
-      <c r="L99" s="2">
-        <v>218</v>
-      </c>
-      <c r="M99" s="2">
-        <v>149</v>
-      </c>
-      <c r="N99" s="2">
-        <v>4268</v>
-      </c>
-      <c r="O99" s="2">
-        <v>4786</v>
-      </c>
-      <c r="P99" s="2">
-        <v>1060</v>
-      </c>
-      <c r="Q99" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R99" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S99" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T99" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>